--- a/delta/dist/20261025_台達電模型_v0.2.1.xlsx
+++ b/delta/dist/20261025_台達電模型_v0.2.1.xlsx
@@ -7036,7 +7036,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7273,7 +7273,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7394,7 +7394,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7515,7 +7515,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7636,7 +7636,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7757,7 +7757,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/delta/dist/20261025_台達電模型_v0.2.1.xlsx
+++ b/delta/dist/20261025_台達電模型_v0.2.1.xlsx
@@ -5704,7 +5704,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5723,7 +5723,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/delta/dist/20261025_台達電模型_v0.2.1.xlsx
+++ b/delta/dist/20261025_台達電模型_v0.2.1.xlsx
@@ -6008,7 +6008,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6027,7 +6027,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6563,7 +6563,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6582,7 +6582,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6727,7 +6727,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6746,7 +6746,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -37335,7 +37335,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>33</v>
@@ -40077,7 +40077,7 @@
       </c>
       <c r="C7" s="20" t="n">
         <f aca="false">PL!D67</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="D7" s="20" t="n">
         <f aca="false">PL!E67</f>
@@ -40104,15 +40104,15 @@
       </c>
       <c r="C8" s="15" t="n">
         <f aca="false">PL!D71</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">PL!E71</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">PL!F71</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="F8" s="15" t="n">
         <f aca="false">PL!G71</f>
@@ -40139,11 +40139,11 @@
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">PL!F72/fx</f>
-        <v>18.8577332859887</v>
+        <v>18.8577332859888</v>
       </c>
       <c r="F9" s="21" t="n">
         <f aca="false">PL!G72/fx</f>
-        <v>21.4819395843786</v>
+        <v>21.4819395843787</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40159,15 +40159,15 @@
       </c>
       <c r="D10" s="21" t="n">
         <f aca="false">PL!E76/fx</f>
-        <v>5.78484809940115</v>
+        <v>5.78484809940116</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">PL!F76/fx</f>
-        <v>7.66628721680113</v>
+        <v>7.66628721680114</v>
       </c>
       <c r="F10" s="21" t="n">
         <f aca="false">PL!G76/fx</f>
-        <v>9.11281373771718</v>
+        <v>9.1128137377172</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>384</v>
@@ -40186,15 +40186,15 @@
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">PL!E76/fx/PL!E65/racks_vr*1000000</f>
-        <v>34.2800338391063</v>
+        <v>34.2800338391064</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">PL!F76/fx/PL!F65/racks_vr*1000000</f>
-        <v>35.8382171954293</v>
+        <v>35.8382171954294</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">PL!G76/fx/PL!G65/racks_vr*1000000</f>
-        <v>37.3964005517523</v>
+        <v>37.3964005517524</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>386</v>
@@ -40213,15 +40213,15 @@
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">PL!E82</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">PL!F82</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">PL!G82</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40233,7 +40233,7 @@
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">PL!D67-PL!D72/fx</f>
-        <v>4.38384793142876</v>
+        <v>4.38384793142875</v>
       </c>
       <c r="D13" s="20" t="n">
         <f aca="false">PL!E67-PL!E72/fx</f>
@@ -40245,7 +40245,7 @@
       </c>
       <c r="F13" s="20" t="n">
         <f aca="false">PL!G67-PL!G72/fx</f>
-        <v>21.8178464656217</v>
+        <v>21.8178464656216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40357,7 +40357,7 @@
       </c>
       <c r="E6" s="15" t="n">
         <f aca="false">E79</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">F79</f>
@@ -40385,15 +40385,15 @@
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">E72</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">F72</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G7" s="20" t="n">
         <f aca="false">G72</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40417,7 +40417,7 @@
       </c>
       <c r="F8" s="20" t="n">
         <f aca="false">F76</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">G76</f>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="F13" s="20" t="n">
         <f aca="false">F93</f>
-        <v>200.402625865529</v>
+        <v>200.40262586553</v>
       </c>
       <c r="G13" s="20" t="n">
         <f aca="false">G93</f>
@@ -40581,7 +40581,7 @@
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">E95</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">F95</f>
@@ -40589,7 +40589,7 @@
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">G95</f>
-        <v>87.1463052676629</v>
+        <v>87.146305267663</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40605,7 +40605,7 @@
       </c>
       <c r="E15" s="15" t="n">
         <f aca="false">E96</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F15" s="15" t="n">
         <f aca="false">F96</f>
@@ -40613,7 +40613,7 @@
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">G96</f>
-        <v>0.129785331867852</v>
+        <v>0.129785331867853</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40662,11 +40662,11 @@
       </c>
       <c r="E19" s="15" t="n">
         <f aca="false">E118</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F19" s="15" t="n">
         <f aca="false">F118</f>
-        <v>0.0670258278455447</v>
+        <v>0.0670258278455449</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">G118</f>
@@ -40690,7 +40690,7 @@
       </c>
       <c r="E20" s="20" t="n">
         <f aca="false">E111</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F20" s="20" t="n">
         <f aca="false">F111</f>
@@ -40698,7 +40698,7 @@
       </c>
       <c r="G20" s="20" t="n">
         <f aca="false">G111</f>
-        <v>584.308756695099</v>
+        <v>584.3087566951</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40726,7 +40726,7 @@
       </c>
       <c r="G21" s="20" t="n">
         <f aca="false">G115</f>
-        <v>247.868533665907</v>
+        <v>247.868533665908</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40886,15 +40886,15 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">E134</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">F134</f>
-        <v>65.5476345626152</v>
+        <v>65.5476345626153</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">G134</f>
-        <v>77.02902230579</v>
+        <v>77.0290223057901</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40910,11 +40910,11 @@
       </c>
       <c r="E28" s="15" t="n">
         <f aca="false">E135</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F28" s="15" t="n">
         <f aca="false">F135</f>
-        <v>0.0795974481975024</v>
+        <v>0.0795974481975026</v>
       </c>
       <c r="G28" s="15" t="n">
         <f aca="false">G135</f>
@@ -40967,15 +40967,15 @@
       </c>
       <c r="E32" s="15" t="n">
         <f aca="false">E157</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F32" s="15" t="n">
         <f aca="false">F157</f>
-        <v>-0.0843228876940264</v>
+        <v>-0.0843228876940263</v>
       </c>
       <c r="G32" s="15" t="n">
         <f aca="false">G157</f>
-        <v>0.0962667561008346</v>
+        <v>0.0962667561008344</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40995,7 +40995,7 @@
       </c>
       <c r="E33" s="20" t="n">
         <f aca="false">E150</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F33" s="20" t="n">
         <f aca="false">F150</f>
@@ -41003,7 +41003,7 @@
       </c>
       <c r="G33" s="20" t="n">
         <f aca="false">G150</f>
-        <v>412.45324002007</v>
+        <v>412.453240020071</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41083,7 +41083,7 @@
       </c>
       <c r="F36" s="15" t="n">
         <f aca="false">F159</f>
-        <v>0.495858354999479</v>
+        <v>0.49585835499948</v>
       </c>
       <c r="G36" s="15" t="n">
         <f aca="false">G159</f>
@@ -41191,7 +41191,7 @@
       </c>
       <c r="E40" s="16" t="n">
         <f aca="false">E173</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F40" s="16" t="n">
         <f aca="false">F173</f>
@@ -41199,7 +41199,7 @@
       </c>
       <c r="G40" s="16" t="n">
         <f aca="false">G173</f>
-        <v>56.4219363298298</v>
+        <v>56.4219363298299</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41215,7 +41215,7 @@
       </c>
       <c r="E41" s="15" t="n">
         <f aca="false">E174</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F41" s="15" t="n">
         <f aca="false">F174</f>
@@ -41303,7 +41303,7 @@
       </c>
       <c r="D63" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -41399,7 +41399,7 @@
       </c>
       <c r="D67" s="21" t="n">
         <f aca="false">D65*D66/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E67" s="21" t="n">
         <f aca="false">E65*E66/1000</f>
@@ -41447,7 +41447,7 @@
       </c>
       <c r="D69" s="15" t="n">
         <f aca="false">a26_aip/D68</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>418</v>
@@ -41486,15 +41486,15 @@
       </c>
       <c r="D71" s="15" t="n">
         <f aca="false">$D$69*D70</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E71" s="15" t="n">
         <f aca="false">$D$69*E70</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F71" s="15" t="n">
         <f aca="false">$D$69*F70</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G71" s="15" t="n">
         <f aca="false">$D$69*G70</f>
@@ -41518,15 +41518,15 @@
       </c>
       <c r="E72" s="20" t="n">
         <f aca="false">E68*E71</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F72" s="20" t="n">
         <f aca="false">F68*F71</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G72" s="20" t="n">
         <f aca="false">G68*G71</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="F76" s="20" t="n">
         <f aca="false">F65*$D$74*F75</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G76" s="20" t="n">
         <f aca="false">G65*$D$74*G75</f>
@@ -41667,7 +41667,7 @@
       </c>
       <c r="E79" s="15" t="n">
         <f aca="false">E78/D78-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F79" s="15" t="n">
         <f aca="false">F78/E78-1</f>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="F80" s="15" t="n">
         <f aca="false">F72/F78</f>
-        <v>0.441588811974854</v>
+        <v>0.441588811974855</v>
       </c>
       <c r="G80" s="15" t="n">
         <f aca="false">G72/G78</f>
@@ -41747,15 +41747,15 @@
       </c>
       <c r="E82" s="19" t="n">
         <f aca="false">(E72+E76)/fx/E65*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F82" s="19" t="n">
         <f aca="false">(F72+F76)/fx/F65*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G82" s="19" t="n">
         <f aca="false">(G72+G76)/fx/G65*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41795,7 +41795,7 @@
       </c>
       <c r="E85" s="20" t="n">
         <f aca="false">$D$84*E78+d_ai*E72</f>
-        <v>417.348687671147</v>
+        <v>417.348687671148</v>
       </c>
       <c r="F85" s="20" t="n">
         <f aca="false">$D$84*F78+d_ai*F72</f>
@@ -41803,7 +41803,7 @@
       </c>
       <c r="G85" s="20" t="n">
         <f aca="false">$D$84*G78+d_ai*G72</f>
-        <v>571.667513908232</v>
+        <v>571.667513908233</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41859,7 +41859,7 @@
       </c>
       <c r="G87" s="20" t="n">
         <f aca="false">F87*(1+MAX(0,phi*G79))</f>
-        <v>251.534257139136</v>
+        <v>251.534257139137</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41887,7 +41887,7 @@
       </c>
       <c r="G88" s="20" t="n">
         <f aca="false">G87+0*G78</f>
-        <v>251.534257139136</v>
+        <v>251.534257139137</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42023,7 +42023,7 @@
       </c>
       <c r="F93" s="20" t="n">
         <f aca="false">(F89+F91)*F92</f>
-        <v>200.402625865529</v>
+        <v>200.40262586553</v>
       </c>
       <c r="G93" s="20" t="n">
         <f aca="false">(G89+G91)*G92</f>
@@ -42075,7 +42075,7 @@
       </c>
       <c r="E95" s="21" t="n">
         <f aca="false">E93/E94</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F95" s="21" t="n">
         <f aca="false">F93/F94</f>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="G95" s="21" t="n">
         <f aca="false">G93/G94</f>
-        <v>87.1463052676629</v>
+        <v>87.146305267663</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42099,7 +42099,7 @@
       </c>
       <c r="E96" s="15" t="n">
         <f aca="false">E95/D95-1</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F96" s="15" t="n">
         <f aca="false">F95/E95-1</f>
@@ -42107,7 +42107,7 @@
       </c>
       <c r="G96" s="15" t="n">
         <f aca="false">G95/F95-1</f>
-        <v>0.129785331867852</v>
+        <v>0.129785331867853</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="D102" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E102" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -42251,7 +42251,7 @@
       </c>
       <c r="D106" s="21" t="n">
         <f aca="false">D104*D105/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E106" s="21" t="n">
         <f aca="false">E104*E105/1000</f>
@@ -42299,7 +42299,7 @@
       </c>
       <c r="D108" s="15" t="n">
         <f aca="false">a26_aip/D107</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H108" s="8" t="s">
         <v>418</v>
@@ -42338,15 +42338,15 @@
       </c>
       <c r="D110" s="15" t="n">
         <f aca="false">$D$108*D109</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E110" s="15" t="n">
         <f aca="false">$D$108*E109</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F110" s="15" t="n">
         <f aca="false">$D$108*F109</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G110" s="15" t="n">
         <f aca="false">$D$108*G109</f>
@@ -42370,7 +42370,7 @@
       </c>
       <c r="E111" s="20" t="n">
         <f aca="false">E107*E110</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F111" s="20" t="n">
         <f aca="false">F107*F110</f>
@@ -42378,7 +42378,7 @@
       </c>
       <c r="G111" s="20" t="n">
         <f aca="false">G107*G110</f>
-        <v>584.308756695099</v>
+        <v>584.3087566951</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42447,7 +42447,7 @@
       </c>
       <c r="G115" s="20" t="n">
         <f aca="false">G104*$D$113*G114</f>
-        <v>247.868533665907</v>
+        <v>247.868533665908</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42519,11 +42519,11 @@
       </c>
       <c r="E118" s="15" t="n">
         <f aca="false">E117/D117-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F118" s="15" t="n">
         <f aca="false">F117/E117-1</f>
-        <v>0.0670258278455447</v>
+        <v>0.0670258278455449</v>
       </c>
       <c r="G118" s="15" t="n">
         <f aca="false">G117/F117-1</f>
@@ -42599,15 +42599,15 @@
       </c>
       <c r="E121" s="19" t="n">
         <f aca="false">(E111+E115)/fx/E104*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F121" s="19" t="n">
         <f aca="false">(F111+F115)/fx/F104*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G121" s="19" t="n">
         <f aca="false">(G111+G115)/fx/G104*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42647,11 +42647,11 @@
       </c>
       <c r="E124" s="20" t="n">
         <f aca="false">$D$123*E117+d_ai*E111</f>
-        <v>417.348687671147</v>
+        <v>417.348687671148</v>
       </c>
       <c r="F124" s="20" t="n">
         <f aca="false">$D$123*F117+d_ai*F111</f>
-        <v>446.094735723176</v>
+        <v>446.094735723177</v>
       </c>
       <c r="G124" s="20" t="n">
         <f aca="false">$D$123*G117+d_ai*G111</f>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="F126" s="20" t="n">
         <f aca="false">E126*(1+MAX(0,phi*F118))</f>
-        <v>207.287269399959</v>
+        <v>207.28726939996</v>
       </c>
       <c r="G126" s="20" t="n">
         <f aca="false">F126*(1+MAX(0,phi*G118))</f>
@@ -42735,7 +42735,7 @@
       </c>
       <c r="F127" s="20" t="n">
         <f aca="false">F126+0*F117</f>
-        <v>207.287269399959</v>
+        <v>207.28726939996</v>
       </c>
       <c r="G127" s="20" t="n">
         <f aca="false">G126+0*G117</f>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="G128" s="20" t="n">
         <f aca="false">G124-G127</f>
-        <v>282.038503380099</v>
+        <v>282.0385033801</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42927,15 +42927,15 @@
       </c>
       <c r="E134" s="21" t="n">
         <f aca="false">E132/E133</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F134" s="21" t="n">
         <f aca="false">F132/F133</f>
-        <v>65.5476345626152</v>
+        <v>65.5476345626153</v>
       </c>
       <c r="G134" s="21" t="n">
         <f aca="false">G132/G133</f>
-        <v>77.02902230579</v>
+        <v>77.0290223057901</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42951,11 +42951,11 @@
       </c>
       <c r="E135" s="15" t="n">
         <f aca="false">E134/D134-1</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F135" s="15" t="n">
         <f aca="false">F134/E134-1</f>
-        <v>0.0795974481975024</v>
+        <v>0.0795974481975026</v>
       </c>
       <c r="G135" s="15" t="n">
         <f aca="false">G134/F134-1</f>
@@ -43007,7 +43007,7 @@
       </c>
       <c r="D141" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E141" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -43103,7 +43103,7 @@
       </c>
       <c r="D145" s="21" t="n">
         <f aca="false">D143*D144/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E145" s="21" t="n">
         <f aca="false">E143*E144/1000</f>
@@ -43151,7 +43151,7 @@
       </c>
       <c r="D147" s="15" t="n">
         <f aca="false">a26_aip/D146</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H147" s="8" t="s">
         <v>418</v>
@@ -43190,15 +43190,15 @@
       </c>
       <c r="D149" s="15" t="n">
         <f aca="false">$D$147*D148</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E149" s="15" t="n">
         <f aca="false">$D$147*E148</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F149" s="15" t="n">
         <f aca="false">$D$147*F148</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G149" s="15" t="n">
         <f aca="false">$D$147*G148</f>
@@ -43222,7 +43222,7 @@
       </c>
       <c r="E150" s="20" t="n">
         <f aca="false">E146*E149</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F150" s="20" t="n">
         <f aca="false">F146*F149</f>
@@ -43230,7 +43230,7 @@
       </c>
       <c r="G150" s="20" t="n">
         <f aca="false">G146*G149</f>
-        <v>412.45324002007</v>
+        <v>412.453240020071</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43371,15 +43371,15 @@
       </c>
       <c r="E157" s="15" t="n">
         <f aca="false">E156/D156-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F157" s="15" t="n">
         <f aca="false">F156/E156-1</f>
-        <v>-0.0843228876940264</v>
+        <v>-0.0843228876940263</v>
       </c>
       <c r="G157" s="15" t="n">
         <f aca="false">G156/F156-1</f>
-        <v>0.0962667561008346</v>
+        <v>0.0962667561008344</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43431,7 +43431,7 @@
       </c>
       <c r="F159" s="15" t="n">
         <f aca="false">(F150+F154)/F156</f>
-        <v>0.495858354999479</v>
+        <v>0.49585835499948</v>
       </c>
       <c r="G159" s="15" t="n">
         <f aca="false">(G150+G154)/G156</f>
@@ -43451,15 +43451,15 @@
       </c>
       <c r="E160" s="19" t="n">
         <f aca="false">(E150+E154)/fx/E143*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F160" s="19" t="n">
         <f aca="false">(F150+F154)/fx/F143*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G160" s="19" t="n">
         <f aca="false">(G150+G154)/fx/G143*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43499,15 +43499,15 @@
       </c>
       <c r="E163" s="20" t="n">
         <f aca="false">$D$162*E156+d_ai*E150</f>
-        <v>417.348687671147</v>
+        <v>417.348687671148</v>
       </c>
       <c r="F163" s="20" t="n">
         <f aca="false">$D$162*F156+d_ai*F150</f>
-        <v>378.642773493488</v>
+        <v>378.642773493489</v>
       </c>
       <c r="G163" s="20" t="n">
         <f aca="false">$D$162*G156+d_ai*G150</f>
-        <v>416.33585325558</v>
+        <v>416.335853255581</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="E173" s="21" t="n">
         <f aca="false">E171/E172</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F173" s="21" t="n">
         <f aca="false">F171/F172</f>
@@ -43787,7 +43787,7 @@
       </c>
       <c r="G173" s="21" t="n">
         <f aca="false">G171/G172</f>
-        <v>56.4219363298298</v>
+        <v>56.4219363298299</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43803,7 +43803,7 @@
       </c>
       <c r="E174" s="15" t="n">
         <f aca="false">E173/D173-1</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F174" s="15" t="n">
         <f aca="false">F173/E173-1</f>
@@ -43916,7 +43916,7 @@
       </c>
       <c r="E181" s="15" t="n">
         <f aca="false">E180/D180-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F181" s="15" t="n">
         <f aca="false">F180/E180-1</f>
@@ -43928,11 +43928,11 @@
       </c>
       <c r="H181" s="25" t="n">
         <f aca="false">$G$181+($C$187-$G$181)*1/3</f>
-        <v>0.0936529302959556</v>
+        <v>0.0936529302959554</v>
       </c>
       <c r="I181" s="25" t="n">
         <f aca="false">$G$181+($C$187-$G$181)*2/3</f>
-        <v>0.0768264651479778</v>
+        <v>0.0768264651479777</v>
       </c>
       <c r="J181" s="25" t="n">
         <f aca="false">$G$181+($C$187-$G$181)*3/3</f>
@@ -43960,7 +43960,7 @@
       </c>
       <c r="F182" s="20" t="n">
         <f aca="false">F93</f>
-        <v>200.402625865529</v>
+        <v>200.40262586553</v>
       </c>
       <c r="G182" s="20" t="n">
         <f aca="false">G93</f>
@@ -44079,7 +44079,7 @@
       </c>
       <c r="E185" s="16" t="n">
         <f aca="false">E95</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F185" s="16" t="n">
         <f aca="false">F95</f>
@@ -44087,11 +44087,11 @@
       </c>
       <c r="G185" s="16" t="n">
         <f aca="false">G95</f>
-        <v>87.1463052676629</v>
+        <v>87.146305267663</v>
       </c>
       <c r="H185" s="27" t="n">
         <f aca="false">H182/H184</f>
-        <v>95.3078121204454</v>
+        <v>95.3078121204455</v>
       </c>
       <c r="I185" s="27" t="n">
         <f aca="false">I182/I184</f>
@@ -44116,7 +44116,7 @@
       </c>
       <c r="E186" s="15" t="n">
         <f aca="false">E185/D185-1</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F186" s="15" t="n">
         <f aca="false">F185/E185-1</f>
@@ -44124,19 +44124,19 @@
       </c>
       <c r="G186" s="15" t="n">
         <f aca="false">G185/F185-1</f>
-        <v>0.129785331867852</v>
+        <v>0.129785331867853</v>
       </c>
       <c r="H186" s="25" t="n">
         <f aca="false">H185/G185-1</f>
-        <v>0.0936529302959557</v>
+        <v>0.0936529302959552</v>
       </c>
       <c r="I186" s="25" t="n">
         <f aca="false">I185/H185-1</f>
-        <v>0.0768264651479778</v>
+        <v>0.076826465147978</v>
       </c>
       <c r="J186" s="25" t="n">
         <f aca="false">J185/I185-1</f>
-        <v>0.0599999999999998</v>
+        <v>0.0600000000000001</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44266,11 +44266,11 @@
       </c>
       <c r="E193" s="15" t="n">
         <f aca="false">E192/D192-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F193" s="15" t="n">
         <f aca="false">F192/E192-1</f>
-        <v>0.0670258278455447</v>
+        <v>0.0670258278455449</v>
       </c>
       <c r="G193" s="15" t="n">
         <f aca="false">G192/F192-1</f>
@@ -44322,7 +44322,7 @@
       </c>
       <c r="I194" s="24" t="n">
         <f aca="false">I192*I195</f>
-        <v>222.938543803738</v>
+        <v>222.938543803739</v>
       </c>
       <c r="J194" s="24" t="n">
         <f aca="false">J192*J195</f>
@@ -44429,27 +44429,27 @@
       </c>
       <c r="E197" s="16" t="n">
         <f aca="false">E134</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F197" s="16" t="n">
         <f aca="false">F134</f>
-        <v>65.5476345626152</v>
+        <v>65.5476345626153</v>
       </c>
       <c r="G197" s="16" t="n">
         <f aca="false">G134</f>
-        <v>77.02902230579</v>
+        <v>77.0290223057901</v>
       </c>
       <c r="H197" s="27" t="n">
         <f aca="false">H194/H196</f>
-        <v>82.666223829496</v>
+        <v>82.6662238294961</v>
       </c>
       <c r="I197" s="27" t="n">
         <f aca="false">I194/I196</f>
-        <v>85.8093869914171</v>
+        <v>85.8093869914172</v>
       </c>
       <c r="J197" s="27" t="n">
         <f aca="false">J194/J196</f>
-        <v>86.0545566685354</v>
+        <v>86.0545566685355</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44466,11 +44466,11 @@
       </c>
       <c r="E198" s="15" t="n">
         <f aca="false">E197/D197-1</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F198" s="15" t="n">
         <f aca="false">F197/E197-1</f>
-        <v>0.0795974481975024</v>
+        <v>0.0795974481975026</v>
       </c>
       <c r="G198" s="15" t="n">
         <f aca="false">G197/F197-1</f>
@@ -44478,11 +44478,11 @@
       </c>
       <c r="H198" s="25" t="n">
         <f aca="false">H197/G197-1</f>
-        <v>0.0731828258357929</v>
+        <v>0.0731828258357932</v>
       </c>
       <c r="I198" s="25" t="n">
         <f aca="false">I197/H197-1</f>
-        <v>0.0380223387051522</v>
+        <v>0.0380223387051524</v>
       </c>
       <c r="J198" s="25" t="n">
         <f aca="false">J197/I197-1</f>
@@ -44616,19 +44616,19 @@
       </c>
       <c r="E205" s="15" t="n">
         <f aca="false">E204/D204-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F205" s="15" t="n">
         <f aca="false">F204/E204-1</f>
-        <v>-0.0843228876940264</v>
+        <v>-0.0843228876940263</v>
       </c>
       <c r="G205" s="15" t="n">
         <f aca="false">G204/F204-1</f>
-        <v>0.0962667561008346</v>
+        <v>0.0962667561008344</v>
       </c>
       <c r="H205" s="25" t="n">
         <f aca="false">$G$205+($C$211-$G$205)*1/3</f>
-        <v>0.0708445040672231</v>
+        <v>0.0708445040672229</v>
       </c>
       <c r="I205" s="25" t="n">
         <f aca="false">$G$205+($C$211-$G$205)*2/3</f>
@@ -44676,7 +44676,7 @@
       </c>
       <c r="J206" s="24" t="n">
         <f aca="false">J204*J207</f>
-        <v>133.908041389923</v>
+        <v>133.908041389924</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44779,7 +44779,7 @@
       </c>
       <c r="E209" s="16" t="n">
         <f aca="false">E173</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F209" s="16" t="n">
         <f aca="false">F173</f>
@@ -44787,11 +44787,11 @@
       </c>
       <c r="G209" s="16" t="n">
         <f aca="false">G173</f>
-        <v>56.4219363298298</v>
+        <v>56.4219363298299</v>
       </c>
       <c r="H209" s="27" t="n">
         <f aca="false">H206/H208</f>
-        <v>56.3911790657871</v>
+        <v>56.3911790657872</v>
       </c>
       <c r="I209" s="27" t="n">
         <f aca="false">I206/I208</f>
@@ -44799,7 +44799,7 @@
       </c>
       <c r="J209" s="27" t="n">
         <f aca="false">J206/J208</f>
-        <v>51.541410241767</v>
+        <v>51.5414102417671</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44816,7 +44816,7 @@
       </c>
       <c r="E210" s="15" t="n">
         <f aca="false">E209/D209-1</f>
-        <v>0.602586283172848</v>
+        <v>0.602586283172849</v>
       </c>
       <c r="F210" s="15" t="n">
         <f aca="false">F209/E209-1</f>
@@ -44832,11 +44832,11 @@
       </c>
       <c r="I210" s="25" t="n">
         <f aca="false">I209/H209-1</f>
-        <v>-0.0292507659687892</v>
+        <v>-0.0292507659687896</v>
       </c>
       <c r="J210" s="25" t="n">
         <f aca="false">J209/I209-1</f>
-        <v>-0.0584615384615386</v>
+        <v>-0.0584615384615385</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44922,11 +44922,11 @@
       </c>
       <c r="E217" s="20" t="n">
         <f aca="false">E182+E180*da_r-E180*cx_r</f>
-        <v>120.847995677372</v>
+        <v>120.847995677373</v>
       </c>
       <c r="F217" s="20" t="n">
         <f aca="false">F182+F180*da_r-F180*cx_r</f>
-        <v>155.452710232915</v>
+        <v>155.452710232916</v>
       </c>
       <c r="G217" s="20" t="n">
         <f aca="false">G182+G180*da_r-G180*cx_r</f>
@@ -44934,11 +44934,11 @@
       </c>
       <c r="H217" s="24" t="n">
         <f aca="false">H182+H180*da_r-H180*cx_r</f>
-        <v>193.025358873164</v>
+        <v>193.025358873165</v>
       </c>
       <c r="I217" s="24" t="n">
         <f aca="false">I182+I180*da_r-I180*cx_r</f>
-        <v>207.854814879309</v>
+        <v>207.85481487931</v>
       </c>
       <c r="J217" s="24" t="n">
         <f aca="false">J182+J180*da_r-J180*cx_r</f>
@@ -44961,7 +44961,7 @@
       </c>
       <c r="E218" s="20" t="n">
         <f aca="false">E194+E192*da_r-E192*cx_r</f>
-        <v>120.847995677372</v>
+        <v>120.847995677373</v>
       </c>
       <c r="F218" s="20" t="n">
         <f aca="false">F194+F192*da_r-F192*cx_r</f>
@@ -44969,7 +44969,7 @@
       </c>
       <c r="G218" s="20" t="n">
         <f aca="false">G194+G192*da_r-G192*cx_r</f>
-        <v>155.041152038063</v>
+        <v>155.041152038064</v>
       </c>
       <c r="H218" s="24" t="n">
         <f aca="false">H194+H192*da_r-H192*cx_r</f>
@@ -45000,11 +45000,11 @@
       </c>
       <c r="E219" s="20" t="n">
         <f aca="false">E206+E204*da_r-E204*cx_r</f>
-        <v>120.847995677372</v>
+        <v>120.847995677373</v>
       </c>
       <c r="F219" s="20" t="n">
         <f aca="false">F206+F204*da_r-F204*cx_r</f>
-        <v>97.2518685077992</v>
+        <v>97.2518685077993</v>
       </c>
       <c r="G219" s="20" t="n">
         <f aca="false">G206+G204*da_r-G204*cx_r</f>
@@ -45328,11 +45328,11 @@
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">PL!E14</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="C23" s="28" t="n">
         <f aca="false">B23</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="D23" s="29" t="n">
         <f aca="false">D17</f>
@@ -45344,7 +45344,7 @@
       </c>
       <c r="F23" s="31" t="n">
         <f aca="false">E23/px-1</f>
-        <v>-0.152639615752336</v>
+        <v>-0.152639615752335</v>
       </c>
       <c r="G23" s="29" t="n">
         <f aca="false">px/C23</f>
@@ -45357,11 +45357,11 @@
       </c>
       <c r="B24" s="28" t="n">
         <f aca="false">PL!E27</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="C24" s="28" t="n">
         <f aca="false">B24</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="D24" s="29" t="n">
         <f aca="false">D18</f>
@@ -45373,7 +45373,7 @@
       </c>
       <c r="F24" s="31" t="n">
         <f aca="false">E24/px-1</f>
-        <v>-0.152639615752336</v>
+        <v>-0.152639615752335</v>
       </c>
       <c r="G24" s="29" t="n">
         <f aca="false">px/C24</f>
@@ -45386,11 +45386,11 @@
       </c>
       <c r="B25" s="28" t="n">
         <f aca="false">PL!E40</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="C25" s="28" t="n">
         <f aca="false">B25</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="D25" s="29" t="n">
         <f aca="false">D19</f>
@@ -45402,7 +45402,7 @@
       </c>
       <c r="F25" s="31" t="n">
         <f aca="false">E25/px-1</f>
-        <v>-0.152639615752336</v>
+        <v>-0.152639615752335</v>
       </c>
       <c r="G25" s="29" t="n">
         <f aca="false">px/C25</f>
@@ -45458,7 +45458,7 @@
       </c>
       <c r="B29" s="18" t="n">
         <f aca="false">px*A29/PL!F14</f>
-        <v>22.8883599515359</v>
+        <v>22.8883599515358</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">px*A29/PL!F40</f>
@@ -45504,7 +45504,7 @@
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">px*A31/PL!F40</f>
-        <v>47.7344351074798</v>
+        <v>47.7344351074797</v>
       </c>
       <c r="D31" s="18" t="n">
         <f aca="false">pe_fair_andy</f>
@@ -45525,7 +45525,7 @@
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">px*A32/PL!F40</f>
-        <v>63.6459134766397</v>
+        <v>63.6459134766396</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">pe_fair_andy</f>
@@ -45575,7 +45575,7 @@
       </c>
       <c r="B37" s="16" t="n">
         <f aca="false">PL!E14</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="C37" s="19" t="n">
         <f aca="false">B37*pe_fair_andy</f>
@@ -45583,7 +45583,7 @@
       </c>
       <c r="D37" s="32" t="n">
         <f aca="false">C37/px-1</f>
-        <v>-0.0542852854378748</v>
+        <v>-0.0542852854378741</v>
       </c>
       <c r="E37" s="16" t="n">
         <f aca="false">PL!F14</f>
@@ -45595,7 +45595,7 @@
       </c>
       <c r="G37" s="32" t="n">
         <f aca="false">F37/px-1</f>
-        <v>0.201484075671166</v>
+        <v>0.201484075671167</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45604,7 +45604,7 @@
       </c>
       <c r="B38" s="16" t="n">
         <f aca="false">PL!E27</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="C38" s="19" t="n">
         <f aca="false">B38*pe_fair_andy</f>
@@ -45612,11 +45612,11 @@
       </c>
       <c r="D38" s="32" t="n">
         <f aca="false">C38/px-1</f>
-        <v>-0.0542852854378748</v>
+        <v>-0.0542852854378741</v>
       </c>
       <c r="E38" s="16" t="n">
         <f aca="false">PL!F27</f>
-        <v>65.5476345626152</v>
+        <v>65.5476345626153</v>
       </c>
       <c r="F38" s="19" t="n">
         <f aca="false">E38*pe_fair_andy</f>
@@ -45624,7 +45624,7 @@
       </c>
       <c r="G38" s="32" t="n">
         <f aca="false">F38/px-1</f>
-        <v>0.0209911925640998</v>
+        <v>0.0209911925641006</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45633,7 +45633,7 @@
       </c>
       <c r="B39" s="16" t="n">
         <f aca="false">PL!E40</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="C39" s="19" t="n">
         <f aca="false">B39*pe_fair_andy</f>
@@ -45641,7 +45641,7 @@
       </c>
       <c r="D39" s="32" t="n">
         <f aca="false">C39/px-1</f>
-        <v>-0.0542852854378748</v>
+        <v>-0.0542852854378741</v>
       </c>
       <c r="E39" s="16" t="n">
         <f aca="false">PL!F40</f>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="G39" s="32" t="n">
         <f aca="false">F39/px-1</f>
-        <v>-0.214403607886753</v>
+        <v>-0.214403607886752</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45681,7 +45681,7 @@
       </c>
       <c r="B43" s="35" t="n">
         <f aca="false">B42/px-1</f>
-        <v>-0.152639615752336</v>
+        <v>-0.152639615752335</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -45999,7 +45999,7 @@
       </c>
       <c r="E78" s="21" t="n">
         <f aca="false">C23</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F78" s="20" t="n">
         <f aca="false">C78*E78</f>
@@ -46007,7 +46007,7 @@
       </c>
       <c r="G78" s="15" t="n">
         <f aca="false">F78/px-1</f>
-        <v>-0.372045429530749</v>
+        <v>-0.372045429530748</v>
       </c>
       <c r="H78" s="16" t="n">
         <f aca="false">px/E78</f>
@@ -46030,7 +46030,7 @@
       </c>
       <c r="E79" s="21" t="n">
         <f aca="false">C23</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F79" s="20" t="n">
         <f aca="false">C79*E79</f>
@@ -46038,7 +46038,7 @@
       </c>
       <c r="G79" s="15" t="n">
         <f aca="false">F79/px-1</f>
-        <v>-0.152639615752336</v>
+        <v>-0.152639615752335</v>
       </c>
       <c r="H79" s="16" t="n">
         <f aca="false">px/E79</f>
@@ -46061,15 +46061,15 @@
       </c>
       <c r="E80" s="21" t="n">
         <f aca="false">C23</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F80" s="20" t="n">
         <f aca="false">C80*E80</f>
-        <v>1472.33595336604</v>
+        <v>1472.33595336605</v>
       </c>
       <c r="G80" s="15" t="n">
         <f aca="false">F80/px-1</f>
-        <v>-0.0826567268747386</v>
+        <v>-0.0826567268747379</v>
       </c>
       <c r="H80" s="16" t="n">
         <f aca="false">px/E80</f>
@@ -46117,15 +46117,15 @@
       </c>
       <c r="B89" s="16" t="n">
         <f aca="false">PL!E185</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="C89" s="16" t="n">
         <f aca="false">PL!E197</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="D89" s="16" t="n">
         <f aca="false">PL!E209</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46138,7 +46138,7 @@
       </c>
       <c r="C90" s="16" t="n">
         <f aca="false">PL!F197</f>
-        <v>65.5476345626152</v>
+        <v>65.5476345626153</v>
       </c>
       <c r="D90" s="16" t="n">
         <f aca="false">PL!F209</f>
@@ -46151,15 +46151,15 @@
       </c>
       <c r="B91" s="16" t="n">
         <f aca="false">PL!G185</f>
-        <v>87.1463052676629</v>
+        <v>87.146305267663</v>
       </c>
       <c r="C91" s="16" t="n">
         <f aca="false">PL!G197</f>
-        <v>77.02902230579</v>
+        <v>77.0290223057901</v>
       </c>
       <c r="D91" s="16" t="n">
         <f aca="false">PL!G209</f>
-        <v>56.4219363298298</v>
+        <v>56.4219363298299</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46168,15 +46168,15 @@
       </c>
       <c r="B92" s="16" t="n">
         <f aca="false">PL!H185</f>
-        <v>95.3078121204454</v>
+        <v>95.3078121204455</v>
       </c>
       <c r="C92" s="16" t="n">
         <f aca="false">PL!H197</f>
-        <v>82.666223829496</v>
+        <v>82.6662238294961</v>
       </c>
       <c r="D92" s="16" t="n">
         <f aca="false">PL!H209</f>
-        <v>56.3911790657871</v>
+        <v>56.3911790657872</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46189,7 +46189,7 @@
       </c>
       <c r="C93" s="16" t="n">
         <f aca="false">PL!I197</f>
-        <v>85.8093869914171</v>
+        <v>85.8093869914172</v>
       </c>
       <c r="D93" s="16" t="n">
         <f aca="false">PL!I209</f>
@@ -46206,11 +46206,11 @@
       </c>
       <c r="C94" s="16" t="n">
         <f aca="false">PL!J197</f>
-        <v>86.0545566685354</v>
+        <v>86.0545566685355</v>
       </c>
       <c r="D94" s="16" t="n">
         <f aca="false">PL!J209</f>
-        <v>51.541410241767</v>
+        <v>51.5414102417671</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46236,15 +46236,15 @@
       </c>
       <c r="B97" s="16" t="n">
         <f aca="false">B89*(1-$B$96)</f>
-        <v>47.356274185364</v>
+        <v>47.3562741853641</v>
       </c>
       <c r="C97" s="16" t="n">
         <f aca="false">C89*(1-$B$96)</f>
-        <v>47.356274185364</v>
+        <v>47.3562741853641</v>
       </c>
       <c r="D97" s="16" t="n">
         <f aca="false">D89*(1-$B$96)</f>
-        <v>47.356274185364</v>
+        <v>47.3562741853641</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46270,7 +46270,7 @@
       </c>
       <c r="B99" s="16" t="n">
         <f aca="false">B91*(1-$B$96)</f>
-        <v>67.9722006983201</v>
+        <v>67.9722006983202</v>
       </c>
       <c r="C99" s="16" t="n">
         <f aca="false">C91*(1-$B$96)</f>
@@ -46278,7 +46278,7 @@
       </c>
       <c r="D99" s="16" t="n">
         <f aca="false">D91*(1-$B$96)</f>
-        <v>44.0078689305273</v>
+        <v>44.0078689305274</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46291,11 +46291,11 @@
       </c>
       <c r="C100" s="16" t="n">
         <f aca="false">C92*(1-$B$96)</f>
-        <v>64.4778357481988</v>
+        <v>64.4778357481989</v>
       </c>
       <c r="D100" s="16" t="n">
         <f aca="false">D92*(1-$B$96)</f>
-        <v>43.9838789413015</v>
+        <v>43.9838789413016</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46304,15 +46304,15 @@
       </c>
       <c r="B101" s="16" t="n">
         <f aca="false">B93*(1-$B$96)</f>
-        <v>80.0491219675386</v>
+        <v>80.0491219675387</v>
       </c>
       <c r="C101" s="16" t="n">
         <f aca="false">C93*(1-$B$96)</f>
-        <v>66.929433857992</v>
+        <v>66.9294338579921</v>
       </c>
       <c r="D101" s="16" t="n">
         <f aca="false">D93*(1-$B$96)</f>
-        <v>42.6973167919899</v>
+        <v>42.69731679199</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46321,15 +46321,15 @@
       </c>
       <c r="B102" s="16" t="n">
         <f aca="false">B94*(1-$B$96)</f>
-        <v>84.8520692855909</v>
+        <v>84.852069285591</v>
       </c>
       <c r="C102" s="16" t="n">
         <f aca="false">C94*(1-$B$96)</f>
-        <v>67.1206608118719</v>
+        <v>67.120660811872</v>
       </c>
       <c r="D102" s="16" t="n">
         <f aca="false">D94*(1-$B$96)</f>
-        <v>40.2011659641505</v>
+        <v>40.2011659641506</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46342,11 +46342,11 @@
       </c>
       <c r="C103" s="19" t="n">
         <f aca="false">SUMPRODUCT(C97:C102,1/(1+tp_r)^{1;2;3;4;5;6})+C102*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
-        <v>910.651482226531</v>
+        <v>910.651482226532</v>
       </c>
       <c r="D103" s="19" t="n">
         <f aca="false">SUMPRODUCT(D97:D102,1/(1+tp_r)^{1;2;3;4;5;6})+D102*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
-        <v>581.208616831908</v>
+        <v>581.208616831909</v>
       </c>
       <c r="E103" s="8" t="s">
         <v>579</v>
@@ -46358,15 +46358,15 @@
       </c>
       <c r="B104" s="19" t="n">
         <f aca="false">B103*(1+tp_r)</f>
-        <v>1234.67030966788</v>
+        <v>1234.67030966789</v>
       </c>
       <c r="C104" s="19" t="n">
         <f aca="false">C103*(1+tp_r)</f>
-        <v>1001.71663044918</v>
+        <v>1001.71663044919</v>
       </c>
       <c r="D104" s="19" t="n">
         <f aca="false">D103*(1+tp_r)</f>
-        <v>639.329478515099</v>
+        <v>639.3294785151</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46375,7 +46375,7 @@
       </c>
       <c r="B105" s="30" t="n">
         <f aca="false">tp_wA*B104+tp_wB*C104+tp_wC*D104</f>
-        <v>999.125303827978</v>
+        <v>999.125303827979</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>582</v>
@@ -46594,7 +46594,7 @@
       </c>
       <c r="B123" s="15" t="n">
         <f aca="false">B120/px-1</f>
-        <v>-0.110021710353809</v>
+        <v>-0.110021710353808</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46603,7 +46603,7 @@
       </c>
       <c r="B124" s="15" t="n">
         <f aca="false">B114/cons_feps-1</f>
-        <v>0.273604015811693</v>
+        <v>0.273604015811694</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>618</v>
@@ -46953,7 +46953,7 @@
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">C8/B8-1</f>
-        <v>0.0681968435021922</v>
+        <v>0.0681968435021931</v>
       </c>
       <c r="E8" s="20" t="n">
         <f aca="false">PL!E117</f>
@@ -46961,7 +46961,7 @@
       </c>
       <c r="F8" s="15" t="n">
         <f aca="false">E8/B8-1</f>
-        <v>0.0681968435021922</v>
+        <v>0.0681968435021931</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">PL!E156</f>
@@ -46969,7 +46969,7 @@
       </c>
       <c r="H8" s="15" t="n">
         <f aca="false">G8/B8-1</f>
-        <v>0.0681968435021922</v>
+        <v>0.0681968435021931</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>649</v>
@@ -46985,27 +46985,27 @@
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">PL!E95</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="D9" s="15" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>-0.0313515527299229</v>
+        <v>-0.0313515527299222</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">PL!E134</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>-0.0313515527299229</v>
+        <v>-0.0313515527299222</v>
       </c>
       <c r="G9" s="21" t="n">
         <f aca="false">PL!E173</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="H9" s="15" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>-0.0313515527299229</v>
+        <v>-0.0313515527299222</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>649</v>
@@ -47021,27 +47021,27 @@
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">PL!E95</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>-0.067359682413388</v>
+        <v>-0.0673596824133873</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">PL!E134</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F10" s="15" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>-0.067359682413388</v>
+        <v>-0.0673596824133873</v>
       </c>
       <c r="G10" s="21" t="n">
         <f aca="false">PL!E173</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="H10" s="15" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>-0.067359682413388</v>
+        <v>-0.0673596824133873</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>647</v>
@@ -47057,27 +47057,27 @@
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">PL!E95</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="D11" s="15" t="n">
         <f aca="false">C11/B11-1</f>
-        <v>-0.248578159964252</v>
+        <v>-0.248578159964251</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">PL!E134</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="F11" s="15" t="n">
         <f aca="false">E11/B11-1</f>
-        <v>-0.248578159964252</v>
+        <v>-0.248578159964251</v>
       </c>
       <c r="G11" s="21" t="n">
         <f aca="false">PL!E173</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="H11" s="15" t="n">
         <f aca="false">G11/B11-1</f>
-        <v>-0.248578159964252</v>
+        <v>-0.248578159964251</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>217</v>
@@ -47092,15 +47092,15 @@
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">PL!E79</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="E12" s="15" t="n">
         <f aca="false">PL!E118</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="G12" s="15" t="n">
         <f aca="false">PL!E157</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>108</v>
@@ -47121,27 +47121,27 @@
       </c>
       <c r="C14" s="20" t="n">
         <f aca="false">PL!D67</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="D14" s="15" t="n">
         <f aca="false">C14/B14-1</f>
-        <v>-0.405096490456002</v>
+        <v>-0.405096490456003</v>
       </c>
       <c r="E14" s="20" t="n">
         <f aca="false">PL!D106</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="F14" s="15" t="n">
         <f aca="false">E14/B14-1</f>
-        <v>-0.405096490456002</v>
+        <v>-0.405096490456003</v>
       </c>
       <c r="G14" s="20" t="n">
         <f aca="false">PL!D145</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="H14" s="15" t="n">
         <f aca="false">G14/B14-1</f>
-        <v>-0.405096490456002</v>
+        <v>-0.405096490456003</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>657</v>
@@ -47196,27 +47196,27 @@
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">PL!D69</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="D16" s="15" t="n">
         <f aca="false">C16-B16</f>
-        <v>-0.116328060603228</v>
+        <v>-0.116328060603227</v>
       </c>
       <c r="E16" s="15" t="n">
         <f aca="false">PL!D108</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="F16" s="15" t="n">
         <f aca="false">E16-B16</f>
-        <v>-0.116328060603228</v>
+        <v>-0.116328060603227</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="false">PL!D147</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H16" s="15" t="n">
         <f aca="false">G16-B16</f>
-        <v>-0.116328060603228</v>
+        <v>-0.116328060603227</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>661</v>
@@ -47231,15 +47231,15 @@
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">PL!E82</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">PL!E121</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="G17" s="19" t="n">
         <f aca="false">PL!E160</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>108</v>
@@ -47258,27 +47258,27 @@
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">Units!D11</f>
-        <v>34.2800338391063</v>
+        <v>34.2800338391064</v>
       </c>
       <c r="D18" s="15" t="n">
         <f aca="false">C18/B18-1</f>
-        <v>-0.387856538587387</v>
+        <v>-0.387856538587386</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">Units!D11</f>
-        <v>34.2800338391063</v>
+        <v>34.2800338391064</v>
       </c>
       <c r="F18" s="15" t="n">
         <f aca="false">E18/B18-1</f>
-        <v>-0.387856538587387</v>
+        <v>-0.387856538587386</v>
       </c>
       <c r="G18" s="19" t="n">
         <f aca="false">Units!D11</f>
-        <v>34.2800338391063</v>
+        <v>34.2800338391064</v>
       </c>
       <c r="H18" s="15" t="n">
         <f aca="false">G18/B18-1</f>
-        <v>-0.387856538587387</v>
+        <v>-0.387856538587386</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>666</v>
@@ -47429,7 +47429,7 @@
       </c>
       <c r="D28" s="15" t="n">
         <f aca="false">C28/B28-1</f>
-        <v>0.273604015811693</v>
+        <v>0.273604015811694</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>301</v>
@@ -47452,7 +47452,7 @@
       </c>
       <c r="D29" s="15" t="n">
         <f aca="false">C29/B29-1</f>
-        <v>-0.514949795650883</v>
+        <v>-0.514949795650882</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>297</v>
@@ -47564,7 +47564,7 @@
       </c>
       <c r="D4" s="20" t="n">
         <f aca="false">PL!E72</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E4" s="15" t="n">
         <f aca="false">PL!E86</f>
@@ -47572,7 +47572,7 @@
       </c>
       <c r="F4" s="16" t="n">
         <f aca="false">PL!E95</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="G4" s="15" t="n">
         <f aca="false">F4/F$4-1</f>
@@ -47584,7 +47584,7 @@
       </c>
       <c r="I4" s="20" t="n">
         <f aca="false">PL!F72</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J4" s="15" t="n">
         <f aca="false">PL!F86</f>
@@ -47612,7 +47612,7 @@
       </c>
       <c r="D5" s="20" t="n">
         <f aca="false">E52</f>
-        <v>396.707352814205</v>
+        <v>396.707352814206</v>
       </c>
       <c r="E5" s="15" t="n">
         <f aca="false">E66</f>
@@ -47624,7 +47624,7 @@
       </c>
       <c r="G5" s="15" t="n">
         <f aca="false">F5/F$4-1</f>
-        <v>-0.0551976242173424</v>
+        <v>-0.0551976242173418</v>
       </c>
       <c r="H5" s="20" t="n">
         <f aca="false">F58</f>
@@ -47632,7 +47632,7 @@
       </c>
       <c r="I5" s="20" t="n">
         <f aca="false">F52</f>
-        <v>469.348028451275</v>
+        <v>469.348028451276</v>
       </c>
       <c r="J5" s="15" t="n">
         <f aca="false">F66</f>
@@ -47640,7 +47640,7 @@
       </c>
       <c r="K5" s="16" t="n">
         <f aca="false">F75</f>
-        <v>67.2423363908845</v>
+        <v>67.2423363908846</v>
       </c>
       <c r="L5" s="15" t="n">
         <f aca="false">K5/K$4-1</f>
@@ -47668,11 +47668,11 @@
       </c>
       <c r="F6" s="16" t="n">
         <f aca="false">E114</f>
-        <v>62.3905433692303</v>
+        <v>62.3905433692304</v>
       </c>
       <c r="G6" s="15" t="n">
         <f aca="false">F6/F$4-1</f>
-        <v>0.027598812108671</v>
+        <v>0.0275988121086712</v>
       </c>
       <c r="H6" s="20" t="n">
         <f aca="false">F97</f>
@@ -47680,7 +47680,7 @@
       </c>
       <c r="I6" s="20" t="n">
         <f aca="false">F91</f>
-        <v>670.497183501822</v>
+        <v>670.497183501823</v>
       </c>
       <c r="J6" s="15" t="n">
         <f aca="false">F105</f>
@@ -47688,11 +47688,11 @@
       </c>
       <c r="K6" s="16" t="n">
         <f aca="false">F114</f>
-        <v>82.0949960365462</v>
+        <v>82.0949960365463</v>
       </c>
       <c r="L6" s="15" t="n">
         <f aca="false">K6/K$4-1</f>
-        <v>0.0642989631857143</v>
+        <v>0.0642989631857147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47720,7 +47720,7 @@
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">F7/F$4-1</f>
-        <v>-0.00689970302716803</v>
+        <v>-0.00689970302716769</v>
       </c>
       <c r="H7" s="20" t="n">
         <f aca="false">F136</f>
@@ -47728,7 +47728,7 @@
       </c>
       <c r="I7" s="20" t="n">
         <f aca="false">F130</f>
-        <v>577.992444369314</v>
+        <v>577.992444369315</v>
       </c>
       <c r="J7" s="15" t="n">
         <f aca="false">F144</f>
@@ -47736,11 +47736,11 @@
       </c>
       <c r="K7" s="16" t="n">
         <f aca="false">F153</f>
-        <v>75.2501720294621</v>
+        <v>75.2501720294622</v>
       </c>
       <c r="L7" s="15" t="n">
         <f aca="false">K7/K$4-1</f>
-        <v>-0.0244389556356135</v>
+        <v>-0.0244389556356136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47756,7 +47756,7 @@
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">E169</f>
-        <v>447.642063837296</v>
+        <v>447.642063837297</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">E183</f>
@@ -47764,11 +47764,11 @@
       </c>
       <c r="F8" s="16" t="n">
         <f aca="false">E192</f>
-        <v>61.0210146286624</v>
+        <v>61.0210146286625</v>
       </c>
       <c r="G8" s="15" t="n">
         <f aca="false">F8/F$4-1</f>
-        <v>0.00504209067369921</v>
+        <v>0.00504209067369965</v>
       </c>
       <c r="H8" s="20" t="n">
         <f aca="false">F175</f>
@@ -47788,7 +47788,7 @@
       </c>
       <c r="L8" s="15" t="n">
         <f aca="false">K8/K$4-1</f>
-        <v>0.0104580992578289</v>
+        <v>0.0104580992578291</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47804,7 +47804,7 @@
       </c>
       <c r="D9" s="20" t="n">
         <f aca="false">E208</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E9" s="15" t="n">
         <f aca="false">E222</f>
@@ -47812,11 +47812,11 @@
       </c>
       <c r="F9" s="16" t="n">
         <f aca="false">E231</f>
-        <v>59.0131712056389</v>
+        <v>59.013171205639</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">F9/F$4-1</f>
-        <v>-0.028027945344239</v>
+        <v>-0.0280279453442384</v>
       </c>
       <c r="H9" s="20" t="n">
         <f aca="false">F214</f>
@@ -47824,7 +47824,7 @@
       </c>
       <c r="I9" s="20" t="n">
         <f aca="false">F208</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J9" s="15" t="n">
         <f aca="false">F222</f>
@@ -47832,11 +47832,11 @@
       </c>
       <c r="K9" s="16" t="n">
         <f aca="false">F231</f>
-        <v>73.7851443702288</v>
+        <v>73.7851443702289</v>
       </c>
       <c r="L9" s="15" t="n">
         <f aca="false">K9/K$4-1</f>
-        <v>-0.0434319210298293</v>
+        <v>-0.0434319210298287</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47852,7 +47852,7 @@
       </c>
       <c r="D10" s="20" t="n">
         <f aca="false">E247</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E10" s="15" t="n">
         <f aca="false">E261</f>
@@ -47872,19 +47872,19 @@
       </c>
       <c r="I10" s="20" t="n">
         <f aca="false">F247</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J10" s="15" t="n">
         <f aca="false">F261</f>
-        <v>0.374474625095646</v>
+        <v>0.374474625095647</v>
       </c>
       <c r="K10" s="16" t="n">
         <f aca="false">F270</f>
-        <v>79.924197793971</v>
+        <v>79.9241977939711</v>
       </c>
       <c r="L10" s="15" t="n">
         <f aca="false">K10/K$4-1</f>
-        <v>0.036156220870097</v>
+        <v>0.0361562208700972</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47900,7 +47900,7 @@
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">E286</f>
-        <v>354.703044869172</v>
+        <v>354.703044869173</v>
       </c>
       <c r="E11" s="15" t="n">
         <f aca="false">E300</f>
@@ -47908,7 +47908,7 @@
       </c>
       <c r="F11" s="16" t="n">
         <f aca="false">E309</f>
-        <v>52.4754968202148</v>
+        <v>52.4754968202149</v>
       </c>
       <c r="G11" s="15" t="n">
         <f aca="false">F11/F$4-1</f>
@@ -47928,7 +47928,7 @@
       </c>
       <c r="K11" s="16" t="n">
         <f aca="false">F309</f>
-        <v>65.7376053485118</v>
+        <v>65.7376053485119</v>
       </c>
       <c r="L11" s="15" t="n">
         <f aca="false">K11/K$4-1</f>
@@ -47948,7 +47948,7 @@
       </c>
       <c r="D12" s="20" t="n">
         <f aca="false">E325</f>
-        <v>532.054567303758</v>
+        <v>532.054567303759</v>
       </c>
       <c r="E12" s="15" t="n">
         <f aca="false">E339</f>
@@ -47960,7 +47960,7 @@
       </c>
       <c r="G12" s="15" t="n">
         <f aca="false">F12/F$4-1</f>
-        <v>0.135706225891612</v>
+        <v>0.135706225891613</v>
       </c>
       <c r="H12" s="20" t="n">
         <f aca="false">F331</f>
@@ -47968,7 +47968,7 @@
       </c>
       <c r="I12" s="20" t="n">
         <f aca="false">F325</f>
-        <v>724.136958181968</v>
+        <v>724.136958181969</v>
       </c>
       <c r="J12" s="15" t="n">
         <f aca="false">F339</f>
@@ -47976,11 +47976,11 @@
       </c>
       <c r="K12" s="16" t="n">
         <f aca="false">F348</f>
-        <v>88.553217298673</v>
+        <v>88.5532172986731</v>
       </c>
       <c r="L12" s="15" t="n">
         <f aca="false">K12/K$4-1</f>
-        <v>0.148024872499914</v>
+        <v>0.148024872499915</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47996,7 +47996,7 @@
       </c>
       <c r="D13" s="20" t="n">
         <f aca="false">E364</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E13" s="15" t="n">
         <f aca="false">E378</f>
@@ -48008,7 +48008,7 @@
       </c>
       <c r="G13" s="15" t="n">
         <f aca="false">F13/F$4-1</f>
-        <v>-0.02324361225715</v>
+        <v>-0.0232436122571494</v>
       </c>
       <c r="H13" s="20" t="n">
         <f aca="false">F370</f>
@@ -48016,19 +48016,19 @@
       </c>
       <c r="I13" s="20" t="n">
         <f aca="false">F364</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J13" s="15" t="n">
         <f aca="false">F378</f>
-        <v>0.377214846258396</v>
+        <v>0.377214846258397</v>
       </c>
       <c r="K13" s="16" t="n">
         <f aca="false">F387</f>
-        <v>74.3832258148109</v>
+        <v>74.383225814811</v>
       </c>
       <c r="L13" s="15" t="n">
         <f aca="false">K13/K$4-1</f>
-        <v>-0.0356782515968475</v>
+        <v>-0.0356782515968469</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="D14" s="20" t="n">
         <f aca="false">E403</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E14" s="15" t="n">
         <f aca="false">E417</f>
@@ -48052,7 +48052,7 @@
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">E426</f>
-        <v>61.6557068333022</v>
+        <v>61.6557068333023</v>
       </c>
       <c r="G14" s="15" t="n">
         <f aca="false">F14/F$4-1</f>
@@ -48064,7 +48064,7 @@
       </c>
       <c r="I14" s="20" t="n">
         <f aca="false">F403</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J14" s="15" t="n">
         <f aca="false">F417</f>
@@ -48072,11 +48072,11 @@
       </c>
       <c r="K14" s="16" t="n">
         <f aca="false">F426</f>
-        <v>79.5094235451528</v>
+        <v>79.5094235451529</v>
       </c>
       <c r="L14" s="15" t="n">
         <f aca="false">K14/K$4-1</f>
-        <v>0.0307789893178005</v>
+        <v>0.0307789893178012</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48092,7 +48092,7 @@
       </c>
       <c r="D15" s="20" t="n">
         <f aca="false">E442</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E15" s="15" t="n">
         <f aca="false">E456</f>
@@ -48112,7 +48112,7 @@
       </c>
       <c r="I15" s="20" t="n">
         <f aca="false">F442</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J15" s="15" t="n">
         <f aca="false">F456</f>
@@ -48120,7 +48120,7 @@
       </c>
       <c r="K15" s="16" t="n">
         <f aca="false">F465</f>
-        <v>74.4991331455169</v>
+        <v>74.499133145517</v>
       </c>
       <c r="L15" s="15" t="n">
         <f aca="false">K15/K$4-1</f>
@@ -48140,7 +48140,7 @@
       </c>
       <c r="D16" s="20" t="n">
         <f aca="false">E481</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E16" s="15" t="n">
         <f aca="false">E495</f>
@@ -48148,11 +48148,11 @@
       </c>
       <c r="F16" s="16" t="n">
         <f aca="false">E504</f>
-        <v>62.3270853367013</v>
+        <v>62.3270853367014</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="false">F16/F$4-1</f>
-        <v>0.0265536312956163</v>
+        <v>0.0265536312956165</v>
       </c>
       <c r="H16" s="20" t="n">
         <f aca="false">F487</f>
@@ -48160,7 +48160,7 @@
       </c>
       <c r="I16" s="20" t="n">
         <f aca="false">F481</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J16" s="15" t="n">
         <f aca="false">F495</f>
@@ -48168,7 +48168,7 @@
       </c>
       <c r="K16" s="16" t="n">
         <f aca="false">F504</f>
-        <v>79.7714221706608</v>
+        <v>79.7714221706609</v>
       </c>
       <c r="L16" s="15" t="n">
         <f aca="false">K16/K$4-1</f>
@@ -48188,7 +48188,7 @@
       </c>
       <c r="D17" s="20" t="n">
         <f aca="false">E520</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E17" s="15" t="n">
         <f aca="false">E534</f>
@@ -48196,7 +48196,7 @@
       </c>
       <c r="F17" s="16" t="n">
         <f aca="false">E543</f>
-        <v>54.757312462751</v>
+        <v>54.7573124627511</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">F17/F$4-1</f>
@@ -48208,7 +48208,7 @@
       </c>
       <c r="I17" s="20" t="n">
         <f aca="false">F520</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="J17" s="15" t="n">
         <f aca="false">F534</f>
@@ -48220,7 +48220,7 @@
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">K17/K$4-1</f>
-        <v>-0.0941016165887308</v>
+        <v>-0.094101616588731</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48236,7 +48236,7 @@
       </c>
       <c r="D18" s="20" t="n">
         <f aca="false">E559</f>
-        <v>230.215918544895</v>
+        <v>230.215918544896</v>
       </c>
       <c r="E18" s="15" t="n">
         <f aca="false">E573</f>
@@ -48244,11 +48244,11 @@
       </c>
       <c r="F18" s="16" t="n">
         <f aca="false">E582</f>
-        <v>53.1546698485424</v>
+        <v>53.1546698485425</v>
       </c>
       <c r="G18" s="15" t="n">
         <f aca="false">F18/F$4-1</f>
-        <v>-0.124519956956666</v>
+        <v>-0.124519956956665</v>
       </c>
       <c r="H18" s="20" t="n">
         <f aca="false">F565</f>
@@ -48284,7 +48284,7 @@
       </c>
       <c r="D19" s="20" t="n">
         <f aca="false">PL!E111</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E19" s="15" t="n">
         <f aca="false">PL!E125</f>
@@ -48292,7 +48292,7 @@
       </c>
       <c r="F19" s="16" t="n">
         <f aca="false">PL!E134</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">F19/F$4-1</f>
@@ -48312,7 +48312,7 @@
       </c>
       <c r="K19" s="16" t="n">
         <f aca="false">PL!F134</f>
-        <v>65.5476345626152</v>
+        <v>65.5476345626153</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">K19/K$4-1</f>
@@ -48332,7 +48332,7 @@
       </c>
       <c r="D20" s="20" t="n">
         <f aca="false">PL!E150</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="E20" s="15" t="n">
         <f aca="false">PL!E164</f>
@@ -48340,7 +48340,7 @@
       </c>
       <c r="F20" s="16" t="n">
         <f aca="false">PL!E173</f>
-        <v>60.7148846748884</v>
+        <v>60.7148846748885</v>
       </c>
       <c r="G20" s="15" t="n">
         <f aca="false">F20/F$4-1</f>
@@ -48417,7 +48417,7 @@
       </c>
       <c r="D43" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E43" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -48513,7 +48513,7 @@
       </c>
       <c r="D47" s="21" t="n">
         <f aca="false">D45*D46/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E47" s="21" t="n">
         <f aca="false">E45*E46/1000</f>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="D49" s="15" t="n">
         <f aca="false">a26_aip/D48</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>418</v>
@@ -48600,7 +48600,7 @@
       </c>
       <c r="D51" s="15" t="n">
         <f aca="false">$D$49*D50</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E51" s="15" t="n">
         <f aca="false">$D$49*E50</f>
@@ -48612,7 +48612,7 @@
       </c>
       <c r="G51" s="15" t="n">
         <f aca="false">$D$49*G50</f>
-        <v>0.379386760607902</v>
+        <v>0.379386760607903</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48632,15 +48632,15 @@
       </c>
       <c r="E52" s="20" t="n">
         <f aca="false">E48*E51</f>
-        <v>396.707352814205</v>
+        <v>396.707352814206</v>
       </c>
       <c r="F52" s="20" t="n">
         <f aca="false">F48*F51</f>
-        <v>469.348028451275</v>
+        <v>469.348028451276</v>
       </c>
       <c r="G52" s="20" t="n">
         <f aca="false">G48*G51</f>
-        <v>525.675698064795</v>
+        <v>525.675698064796</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48705,7 +48705,7 @@
       </c>
       <c r="F56" s="20" t="n">
         <f aca="false">F45*$D$54*F55</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G56" s="20" t="n">
         <f aca="false">G45*$D$54*G55</f>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="E59" s="15" t="n">
         <f aca="false">E58/D58-1</f>
-        <v>0.421075183379376</v>
+        <v>0.421075183379377</v>
       </c>
       <c r="F59" s="15" t="n">
         <f aca="false">F58/E58-1</f>
@@ -48789,7 +48789,7 @@
       </c>
       <c r="G59" s="15" t="n">
         <f aca="false">G58/F58-1</f>
-        <v>0.100067746795722</v>
+        <v>0.100067746795723</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48813,7 +48813,7 @@
       </c>
       <c r="F60" s="15" t="n">
         <f aca="false">F52/F58</f>
-        <v>0.380829041293884</v>
+        <v>0.380829041293885</v>
       </c>
       <c r="G60" s="15" t="n">
         <f aca="false">G52/G58</f>
@@ -48841,7 +48841,7 @@
       </c>
       <c r="F61" s="15" t="n">
         <f aca="false">(F52+F56)/F58</f>
-        <v>0.579882682282072</v>
+        <v>0.579882682282073</v>
       </c>
       <c r="G61" s="15" t="n">
         <f aca="false">(G52+G56)/G58</f>
@@ -48865,11 +48865,11 @@
       </c>
       <c r="F62" s="19" t="n">
         <f aca="false">(F52+F56)/fx/F45*1000</f>
-        <v>423.044299228743</v>
+        <v>423.044299228744</v>
       </c>
       <c r="G62" s="19" t="n">
         <f aca="false">(G52+G56)/fx/G45*1000</f>
-        <v>424.68868267339</v>
+        <v>424.688682673391</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48917,7 +48917,7 @@
       </c>
       <c r="G65" s="20" t="n">
         <f aca="false">$D$64*G58+d_ai*G52</f>
-        <v>503.657303742673</v>
+        <v>503.657303742674</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49049,7 +49049,7 @@
       </c>
       <c r="E70" s="15" t="n">
         <f aca="false">E69/E58</f>
-        <v>0.193492474649934</v>
+        <v>0.193492474649935</v>
       </c>
       <c r="F70" s="15" t="n">
         <f aca="false">F69/F58</f>
@@ -49133,7 +49133,7 @@
       </c>
       <c r="E73" s="20" t="n">
         <f aca="false">(E69+E71)*E72</f>
-        <v>149.034395962453</v>
+        <v>149.034395962454</v>
       </c>
       <c r="F73" s="20" t="n">
         <f aca="false">(F69+F71)*F72</f>
@@ -49193,11 +49193,11 @@
       </c>
       <c r="F75" s="21" t="n">
         <f aca="false">F73/F74</f>
-        <v>67.2423363908845</v>
+        <v>67.2423363908846</v>
       </c>
       <c r="G75" s="21" t="n">
         <f aca="false">G73/G74</f>
-        <v>75.0840925031324</v>
+        <v>75.0840925031325</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49213,7 +49213,7 @@
       </c>
       <c r="E76" s="15" t="n">
         <f aca="false">E75/D75-1</f>
-        <v>0.514127327738405</v>
+        <v>0.514127327738408</v>
       </c>
       <c r="F76" s="15" t="n">
         <f aca="false">F75/E75-1</f>
@@ -49221,7 +49221,7 @@
       </c>
       <c r="G76" s="15" t="n">
         <f aca="false">G75/F75-1</f>
-        <v>0.116619328434147</v>
+        <v>0.116619328434146</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49269,7 +49269,7 @@
       </c>
       <c r="D82" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E82" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -49365,7 +49365,7 @@
       </c>
       <c r="D86" s="21" t="n">
         <f aca="false">D84*D85/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E86" s="21" t="n">
         <f aca="false">E84*E85/1000</f>
@@ -49413,7 +49413,7 @@
       </c>
       <c r="D88" s="15" t="n">
         <f aca="false">a26_aip/D87</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H88" s="8" t="s">
         <v>418</v>
@@ -49452,19 +49452,19 @@
       </c>
       <c r="D90" s="15" t="n">
         <f aca="false">$D$88*D89</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E90" s="15" t="n">
         <f aca="false">$D$88*E89</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="F90" s="15" t="n">
         <f aca="false">$D$88*F89</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="G90" s="15" t="n">
         <f aca="false">$D$88*G89</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49488,11 +49488,11 @@
       </c>
       <c r="F91" s="20" t="n">
         <f aca="false">F87*F90</f>
-        <v>670.497183501822</v>
+        <v>670.497183501823</v>
       </c>
       <c r="G91" s="20" t="n">
         <f aca="false">G87*G90</f>
-        <v>808.731843176608</v>
+        <v>808.731843176609</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49557,7 +49557,7 @@
       </c>
       <c r="F95" s="20" t="n">
         <f aca="false">F84*$D$93*F94</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G95" s="20" t="n">
         <f aca="false">G84*$D$93*G94</f>
@@ -49633,7 +49633,7 @@
       </c>
       <c r="E98" s="15" t="n">
         <f aca="false">E97/D97-1</f>
-        <v>0.513625378988463</v>
+        <v>0.513625378988465</v>
       </c>
       <c r="F98" s="15" t="n">
         <f aca="false">F97/E97-1</f>
@@ -49665,7 +49665,7 @@
       </c>
       <c r="F99" s="15" t="n">
         <f aca="false">F91/F97</f>
-        <v>0.467706040549852</v>
+        <v>0.467706040549853</v>
       </c>
       <c r="G99" s="15" t="n">
         <f aca="false">G91/G97</f>
@@ -49713,11 +49713,11 @@
       </c>
       <c r="E101" s="19" t="n">
         <f aca="false">(E91+E95)/fx/E84*1000</f>
-        <v>489.105860754122</v>
+        <v>489.105860754123</v>
       </c>
       <c r="F101" s="19" t="n">
         <f aca="false">(F91+F95)/fx/F84*1000</f>
-        <v>542.113374865685</v>
+        <v>542.113374865686</v>
       </c>
       <c r="G101" s="19" t="n">
         <f aca="false">(G91+G95)/fx/G84*1000</f>
@@ -49765,7 +49765,7 @@
       </c>
       <c r="F104" s="20" t="n">
         <f aca="false">$D$103*F97+d_ai*F91</f>
-        <v>541.739389232497</v>
+        <v>541.739389232498</v>
       </c>
       <c r="G104" s="20" t="n">
         <f aca="false">$D$103*G97+d_ai*G91</f>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="F108" s="20" t="n">
         <f aca="false">F104-F107</f>
-        <v>301.113488301996</v>
+        <v>301.113488301997</v>
       </c>
       <c r="G108" s="20" t="n">
         <f aca="false">G104-G107</f>
@@ -50041,11 +50041,11 @@
       </c>
       <c r="E114" s="21" t="n">
         <f aca="false">E112/E113</f>
-        <v>62.3905433692303</v>
+        <v>62.3905433692304</v>
       </c>
       <c r="F114" s="21" t="n">
         <f aca="false">F112/F113</f>
-        <v>82.0949960365462</v>
+        <v>82.0949960365463</v>
       </c>
       <c r="G114" s="21" t="n">
         <f aca="false">G112/G113</f>
@@ -50065,7 +50065,7 @@
       </c>
       <c r="E115" s="15" t="n">
         <f aca="false">E114/D114-1</f>
-        <v>0.646815760890069</v>
+        <v>0.64681576089007</v>
       </c>
       <c r="F115" s="15" t="n">
         <f aca="false">F114/E114-1</f>
@@ -50121,7 +50121,7 @@
       </c>
       <c r="D121" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E121" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -50217,7 +50217,7 @@
       </c>
       <c r="D125" s="21" t="n">
         <f aca="false">D123*D124/1000</f>
-        <v>8.89182445598429</v>
+        <v>8.89182445598428</v>
       </c>
       <c r="E125" s="21" t="n">
         <f aca="false">E123*E124/1000</f>
@@ -50308,7 +50308,7 @@
       </c>
       <c r="E129" s="15" t="n">
         <f aca="false">$D$127*E128</f>
-        <v>0.656630931821369</v>
+        <v>0.65663093182137</v>
       </c>
       <c r="F129" s="15" t="n">
         <f aca="false">$D$127*F128</f>
@@ -50316,7 +50316,7 @@
       </c>
       <c r="G129" s="15" t="n">
         <f aca="false">$D$127*G128</f>
-        <v>0.587511886366488</v>
+        <v>0.587511886366489</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50340,11 +50340,11 @@
       </c>
       <c r="F130" s="20" t="n">
         <f aca="false">F126*F129</f>
-        <v>577.992444369314</v>
+        <v>577.992444369315</v>
       </c>
       <c r="G130" s="20" t="n">
         <f aca="false">G126*G129</f>
-        <v>621.845619547803</v>
+        <v>621.845619547804</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50409,7 +50409,7 @@
       </c>
       <c r="F134" s="20" t="n">
         <f aca="false">F123*$D$132*F133</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G134" s="20" t="n">
         <f aca="false">G123*$D$132*G133</f>
@@ -50485,7 +50485,7 @@
       </c>
       <c r="E137" s="15" t="n">
         <f aca="false">E136/D136-1</f>
-        <v>0.475062797484677</v>
+        <v>0.475062797484678</v>
       </c>
       <c r="F137" s="15" t="n">
         <f aca="false">F136/E136-1</f>
@@ -50493,7 +50493,7 @@
       </c>
       <c r="G137" s="15" t="n">
         <f aca="false">G136/F136-1</f>
-        <v>0.08265919451022</v>
+        <v>0.0826591945102202</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50513,7 +50513,7 @@
       </c>
       <c r="E138" s="15" t="n">
         <f aca="false">E130/E136</f>
-        <v>0.392145150391679</v>
+        <v>0.39214515039168</v>
       </c>
       <c r="F138" s="15" t="n">
         <f aca="false">F130/F136</f>
@@ -50541,7 +50541,7 @@
       </c>
       <c r="E139" s="15" t="n">
         <f aca="false">(E130+E134)/E136</f>
-        <v>0.558052714018928</v>
+        <v>0.558052714018929</v>
       </c>
       <c r="F139" s="15" t="n">
         <f aca="false">(F130+F134)/F136</f>
@@ -50565,11 +50565,11 @@
       </c>
       <c r="E140" s="19" t="n">
         <f aca="false">(E130+E134)/fx/E123*1000</f>
-        <v>467.218163026743</v>
+        <v>467.218163026744</v>
       </c>
       <c r="F140" s="19" t="n">
         <f aca="false">(F130+F134)/fx/F123*1000</f>
-        <v>487.35573107754</v>
+        <v>487.355731077541</v>
       </c>
       <c r="G140" s="19" t="n">
         <f aca="false">(G130+G134)/fx/G123*1000</f>
@@ -50621,7 +50621,7 @@
       </c>
       <c r="G143" s="20" t="n">
         <f aca="false">$D$142*G136+d_ai*G130</f>
-        <v>544.094295477623</v>
+        <v>544.094295477624</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50677,7 +50677,7 @@
       </c>
       <c r="G145" s="20" t="n">
         <f aca="false">F145*(1+MAX(0,phi*G137))</f>
-        <v>242.547108319936</v>
+        <v>242.547108319937</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50705,7 +50705,7 @@
       </c>
       <c r="G146" s="20" t="n">
         <f aca="false">G145+0*G136</f>
-        <v>242.547108319936</v>
+        <v>242.547108319937</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50725,11 +50725,11 @@
       </c>
       <c r="E147" s="20" t="n">
         <f aca="false">E143-E146</f>
-        <v>219.033297003365</v>
+        <v>219.033297003366</v>
       </c>
       <c r="F147" s="20" t="n">
         <f aca="false">F143-F146</f>
-        <v>275.340572438755</v>
+        <v>275.340572438756</v>
       </c>
       <c r="G147" s="20" t="n">
         <f aca="false">G143-G146</f>
@@ -50897,11 +50897,11 @@
       </c>
       <c r="F153" s="21" t="n">
         <f aca="false">F151/F152</f>
-        <v>75.2501720294621</v>
+        <v>75.2501720294622</v>
       </c>
       <c r="G153" s="21" t="n">
         <f aca="false">G151/G152</f>
-        <v>82.2101786707125</v>
+        <v>82.2101786707126</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50917,15 +50917,15 @@
       </c>
       <c r="E154" s="15" t="n">
         <f aca="false">E153/D153-1</f>
-        <v>0.591528913743542</v>
+        <v>0.591528913743544</v>
       </c>
       <c r="F154" s="15" t="n">
         <f aca="false">F153/E153-1</f>
-        <v>0.248013292228917</v>
+        <v>0.248013292228916</v>
       </c>
       <c r="G154" s="15" t="n">
         <f aca="false">G153/F153-1</f>
-        <v>0.0924915711624603</v>
+        <v>0.0924915711624608</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50973,7 +50973,7 @@
       </c>
       <c r="D160" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E160" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -51093,7 +51093,7 @@
       </c>
       <c r="D165" s="20" t="n">
         <f aca="false">D164*fx</f>
-        <v>389.368313019944</v>
+        <v>389.368313019943</v>
       </c>
       <c r="E165" s="20" t="n">
         <f aca="false">E164*fx</f>
@@ -51160,7 +51160,7 @@
       </c>
       <c r="E168" s="15" t="n">
         <f aca="false">$D$166*E167</f>
-        <v>0.479845680946385</v>
+        <v>0.479845680946386</v>
       </c>
       <c r="F168" s="15" t="n">
         <f aca="false">$D$166*F167</f>
@@ -51168,7 +51168,7 @@
       </c>
       <c r="G168" s="15" t="n">
         <f aca="false">$D$166*G167</f>
-        <v>0.429335609267818</v>
+        <v>0.429335609267819</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51188,7 +51188,7 @@
       </c>
       <c r="E169" s="20" t="n">
         <f aca="false">E165*E168</f>
-        <v>447.642063837296</v>
+        <v>447.642063837297</v>
       </c>
       <c r="F169" s="20" t="n">
         <f aca="false">F165*F168</f>
@@ -51196,7 +51196,7 @@
       </c>
       <c r="G169" s="20" t="n">
         <f aca="false">G165*G168</f>
-        <v>702.294178720071</v>
+        <v>702.294178720072</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51261,7 +51261,7 @@
       </c>
       <c r="F173" s="20" t="n">
         <f aca="false">F162*$D$171*F172</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G173" s="20" t="n">
         <f aca="false">G162*$D$171*G172</f>
@@ -51337,7 +51337,7 @@
       </c>
       <c r="E176" s="15" t="n">
         <f aca="false">E175/D175-1</f>
-        <v>0.488411383389833</v>
+        <v>0.488411383389835</v>
       </c>
       <c r="F176" s="15" t="n">
         <f aca="false">F175/E175-1</f>
@@ -51369,7 +51369,7 @@
       </c>
       <c r="F177" s="15" t="n">
         <f aca="false">F169/F175</f>
-        <v>0.446016556601534</v>
+        <v>0.446016556601535</v>
       </c>
       <c r="G177" s="15" t="n">
         <f aca="false">G169/G175</f>
@@ -51417,15 +51417,15 @@
       </c>
       <c r="E179" s="19" t="n">
         <f aca="false">(E169+E173)/fx/E162*1000</f>
-        <v>474.794673778528</v>
+        <v>474.794673778529</v>
       </c>
       <c r="F179" s="19" t="n">
         <f aca="false">(F169+F173)/fx/F162*1000</f>
-        <v>508.888972161561</v>
+        <v>508.888972161562</v>
       </c>
       <c r="G179" s="19" t="n">
         <f aca="false">(G169+G173)/fx/G162*1000</f>
-        <v>516.465482913346</v>
+        <v>516.465482913347</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51465,11 +51465,11 @@
       </c>
       <c r="E182" s="20" t="n">
         <f aca="false">$D$181*E175+d_ai*E169</f>
-        <v>419.141278491394</v>
+        <v>419.141278491395</v>
       </c>
       <c r="F182" s="20" t="n">
         <f aca="false">$D$181*F175+d_ai*F169</f>
-        <v>518.139172550451</v>
+        <v>518.139172550452</v>
       </c>
       <c r="G182" s="20" t="n">
         <f aca="false">$D$181*G175+d_ai*G169</f>
@@ -51501,7 +51501,7 @@
       </c>
       <c r="G183" s="15" t="n">
         <f aca="false">G182/G175</f>
-        <v>0.377138568994548</v>
+        <v>0.377138568994549</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51525,7 +51525,7 @@
       </c>
       <c r="F184" s="20" t="n">
         <f aca="false">E184*(1+MAX(0,phi*F176))</f>
-        <v>232.663148755725</v>
+        <v>232.663148755726</v>
       </c>
       <c r="G184" s="20" t="n">
         <f aca="false">F184*(1+MAX(0,phi*G176))</f>
@@ -51553,7 +51553,7 @@
       </c>
       <c r="F185" s="20" t="n">
         <f aca="false">F184+0*F175</f>
-        <v>232.663148755725</v>
+        <v>232.663148755726</v>
       </c>
       <c r="G185" s="20" t="n">
         <f aca="false">G184+0*G175</f>
@@ -51745,7 +51745,7 @@
       </c>
       <c r="E192" s="21" t="n">
         <f aca="false">E190/E191</f>
-        <v>61.0210146286624</v>
+        <v>61.0210146286625</v>
       </c>
       <c r="F192" s="21" t="n">
         <f aca="false">F190/F191</f>
@@ -51753,7 +51753,7 @@
       </c>
       <c r="G192" s="21" t="n">
         <f aca="false">G190/G191</f>
-        <v>88.2591393781273</v>
+        <v>88.2591393781275</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51769,7 +51769,7 @@
       </c>
       <c r="E193" s="15" t="n">
         <f aca="false">E192/D192-1</f>
-        <v>0.610666668525032</v>
+        <v>0.610666668525034</v>
       </c>
       <c r="F193" s="15" t="n">
         <f aca="false">F192/E192-1</f>
@@ -51825,7 +51825,7 @@
       </c>
       <c r="D199" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E199" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -51921,7 +51921,7 @@
       </c>
       <c r="D203" s="21" t="n">
         <f aca="false">D201*D202/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E203" s="21" t="n">
         <f aca="false">E201*E202/1000</f>
@@ -51969,7 +51969,7 @@
       </c>
       <c r="D205" s="15" t="n">
         <f aca="false">a26_aip/D204</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H205" s="8" t="s">
         <v>418</v>
@@ -52008,15 +52008,15 @@
       </c>
       <c r="D207" s="15" t="n">
         <f aca="false">$D$205*D206</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E207" s="15" t="n">
         <f aca="false">$D$205*E206</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F207" s="15" t="n">
         <f aca="false">$D$205*F206</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G207" s="15" t="n">
         <f aca="false">$D$205*G206</f>
@@ -52040,15 +52040,15 @@
       </c>
       <c r="E208" s="20" t="n">
         <f aca="false">E204*E207</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F208" s="20" t="n">
         <f aca="false">F204*F207</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G208" s="20" t="n">
         <f aca="false">G204*G207</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52109,11 +52109,11 @@
       </c>
       <c r="E212" s="20" t="n">
         <f aca="false">E201*$D$210*E211</f>
-        <v>151.457841147957</v>
+        <v>151.457841147958</v>
       </c>
       <c r="F212" s="20" t="n">
         <f aca="false">F201*$D$210*F211</f>
-        <v>181.324358519122</v>
+        <v>181.324358519123</v>
       </c>
       <c r="G212" s="20" t="n">
         <f aca="false">G201*$D$210*G211</f>
@@ -52189,15 +52189,15 @@
       </c>
       <c r="E215" s="15" t="n">
         <f aca="false">E214/D214-1</f>
-        <v>0.438280027434911</v>
+        <v>0.438280027434912</v>
       </c>
       <c r="F215" s="15" t="n">
         <f aca="false">F214/E214-1</f>
-        <v>0.197243379052275</v>
+        <v>0.197243379052276</v>
       </c>
       <c r="G215" s="15" t="n">
         <f aca="false">G214/F214-1</f>
-        <v>0.0904138475713114</v>
+        <v>0.090413847571311</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52249,11 +52249,11 @@
       </c>
       <c r="F217" s="15" t="n">
         <f aca="false">(F208+F212)/F214</f>
-        <v>0.602493361055005</v>
+        <v>0.602493361055006</v>
       </c>
       <c r="G217" s="15" t="n">
         <f aca="false">(G208+G212)/G214</f>
-        <v>0.620871556773073</v>
+        <v>0.620871556773074</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52273,11 +52273,11 @@
       </c>
       <c r="F218" s="19" t="n">
         <f aca="false">(F208+F212)/fx/F201*1000</f>
-        <v>464.541129227779</v>
+        <v>464.54112922778</v>
       </c>
       <c r="G218" s="19" t="n">
         <f aca="false">(G208+G212)/fx/G201*1000</f>
-        <v>458.227370267958</v>
+        <v>458.227370267959</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52321,7 +52321,7 @@
       </c>
       <c r="F221" s="20" t="n">
         <f aca="false">$D$220*F214+d_ai*F208</f>
-        <v>491.757413701106</v>
+        <v>491.757413701107</v>
       </c>
       <c r="G221" s="20" t="n">
         <f aca="false">$D$220*G214+d_ai*G208</f>
@@ -52545,11 +52545,11 @@
       </c>
       <c r="F229" s="20" t="n">
         <f aca="false">(F225+F227)*F228</f>
-        <v>191.698754844767</v>
+        <v>191.698754844768</v>
       </c>
       <c r="G229" s="20" t="n">
         <f aca="false">(G225+G227)*G228</f>
-        <v>212.924662324356</v>
+        <v>212.924662324357</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52597,15 +52597,15 @@
       </c>
       <c r="E231" s="21" t="n">
         <f aca="false">E229/E230</f>
-        <v>59.0131712056389</v>
+        <v>59.013171205639</v>
       </c>
       <c r="F231" s="21" t="n">
         <f aca="false">F229/F230</f>
-        <v>73.7851443702288</v>
+        <v>73.7851443702289</v>
       </c>
       <c r="G231" s="21" t="n">
         <f aca="false">G229/G230</f>
-        <v>81.9550286714536</v>
+        <v>81.9550286714537</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52621,7 +52621,7 @@
       </c>
       <c r="E232" s="15" t="n">
         <f aca="false">E231/D231-1</f>
-        <v>0.557669082418652</v>
+        <v>0.557669082418654</v>
       </c>
       <c r="F232" s="15" t="n">
         <f aca="false">F231/E231-1</f>
@@ -52677,7 +52677,7 @@
       </c>
       <c r="D238" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E238" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -52773,7 +52773,7 @@
       </c>
       <c r="D242" s="21" t="n">
         <f aca="false">D240*D241/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E242" s="21" t="n">
         <f aca="false">E240*E241/1000</f>
@@ -52821,7 +52821,7 @@
       </c>
       <c r="D244" s="15" t="n">
         <f aca="false">a26_aip/D243</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H244" s="8" t="s">
         <v>418</v>
@@ -52860,15 +52860,15 @@
       </c>
       <c r="D246" s="15" t="n">
         <f aca="false">$D$244*D245</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E246" s="15" t="n">
         <f aca="false">$D$244*E245</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F246" s="15" t="n">
         <f aca="false">$D$244*F245</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G246" s="15" t="n">
         <f aca="false">$D$244*G245</f>
@@ -52892,15 +52892,15 @@
       </c>
       <c r="E247" s="20" t="n">
         <f aca="false">E243*E246</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F247" s="20" t="n">
         <f aca="false">F243*F246</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G247" s="20" t="n">
         <f aca="false">G243*G246</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52961,15 +52961,15 @@
       </c>
       <c r="E251" s="20" t="n">
         <f aca="false">E240*$D$249*E250</f>
-        <v>218.772437213716</v>
+        <v>218.772437213717</v>
       </c>
       <c r="F251" s="20" t="n">
         <f aca="false">F240*$D$249*F250</f>
-        <v>298.651884619731</v>
+        <v>298.651884619732</v>
       </c>
       <c r="G251" s="20" t="n">
         <f aca="false">G240*$D$249*G250</f>
-        <v>364.512549508687</v>
+        <v>364.512549508688</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53025,7 +53025,7 @@
       </c>
       <c r="G253" s="20" t="n">
         <f aca="false">G247+G251+G252</f>
-        <v>1590.41372873652</v>
+        <v>1590.41372873653</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53041,11 +53041,11 @@
       </c>
       <c r="E254" s="15" t="n">
         <f aca="false">E253/D253-1</f>
-        <v>0.527270600135957</v>
+        <v>0.527270600135958</v>
       </c>
       <c r="F254" s="15" t="n">
         <f aca="false">F253/E253-1</f>
-        <v>0.229041801027937</v>
+        <v>0.229041801027938</v>
       </c>
       <c r="G254" s="15" t="n">
         <f aca="false">G253/F253-1</f>
@@ -53097,7 +53097,7 @@
       </c>
       <c r="E256" s="15" t="n">
         <f aca="false">(E247+E251)/E253</f>
-        <v>0.573160119796735</v>
+        <v>0.573160119796736</v>
       </c>
       <c r="F256" s="15" t="n">
         <f aca="false">(F247+F251)/F253</f>
@@ -53105,7 +53105,7 @@
       </c>
       <c r="G256" s="15" t="n">
         <f aca="false">(G247+G251)/G253</f>
-        <v>0.661421991775998</v>
+        <v>0.661421991775999</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53121,15 +53121,15 @@
       </c>
       <c r="E257" s="19" t="n">
         <f aca="false">(E247+E251)/fx/E240*1000</f>
-        <v>496.850738411502</v>
+        <v>496.850738411503</v>
       </c>
       <c r="F257" s="19" t="n">
         <f aca="false">(F247+F251)/fx/F240*1000</f>
-        <v>533.992477785809</v>
+        <v>533.99247778581</v>
       </c>
       <c r="G257" s="19" t="n">
         <f aca="false">(G247+G251)/fx/G240*1000</f>
-        <v>546.61999570545</v>
+        <v>546.619995705451</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53173,11 +53173,11 @@
       </c>
       <c r="F260" s="20" t="n">
         <f aca="false">$D$259*F253+d_ai*F247</f>
-        <v>531.704434829328</v>
+        <v>531.704434829329</v>
       </c>
       <c r="G260" s="20" t="n">
         <f aca="false">$D$259*G253+d_ai*G247</f>
-        <v>596.488953515233</v>
+        <v>596.488953515234</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53201,7 +53201,7 @@
       </c>
       <c r="F261" s="15" t="n">
         <f aca="false">F260/F253</f>
-        <v>0.374474625095646</v>
+        <v>0.374474625095647</v>
       </c>
       <c r="G261" s="15" t="n">
         <f aca="false">G260/G253</f>
@@ -53233,7 +53233,7 @@
       </c>
       <c r="G262" s="20" t="n">
         <f aca="false">F262*(1+MAX(0,phi*G254))</f>
-        <v>261.707871218786</v>
+        <v>261.707871218787</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53261,7 +53261,7 @@
       </c>
       <c r="G263" s="20" t="n">
         <f aca="false">G262+0*G253</f>
-        <v>261.707871218786</v>
+        <v>261.707871218787</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53401,7 +53401,7 @@
       </c>
       <c r="G268" s="20" t="n">
         <f aca="false">(G264+G266)*G267</f>
-        <v>236.518946784548</v>
+        <v>236.518946784549</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53453,11 +53453,11 @@
       </c>
       <c r="F270" s="21" t="n">
         <f aca="false">F268/F269</f>
-        <v>79.924197793971</v>
+        <v>79.9241977939711</v>
       </c>
       <c r="G270" s="21" t="n">
         <f aca="false">G268/G269</f>
-        <v>91.0365049002233</v>
+        <v>91.0365049002234</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53473,7 +53473,7 @@
       </c>
       <c r="E271" s="15" t="n">
         <f aca="false">E270/D270-1</f>
-        <v>0.647503483927043</v>
+        <v>0.647503483927044</v>
       </c>
       <c r="F271" s="15" t="n">
         <f aca="false">F270/E270-1</f>
@@ -53529,7 +53529,7 @@
       </c>
       <c r="D277" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E277" s="21" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -53625,7 +53625,7 @@
       </c>
       <c r="D281" s="21" t="n">
         <f aca="false">D279*D280/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E281" s="21" t="n">
         <f aca="false">E279*E280/1000</f>
@@ -53673,7 +53673,7 @@
       </c>
       <c r="D283" s="15" t="n">
         <f aca="false">a26_aip/D282</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H283" s="8" t="s">
         <v>418</v>
@@ -53712,15 +53712,15 @@
       </c>
       <c r="D285" s="15" t="n">
         <f aca="false">$D$283*D284</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E285" s="15" t="n">
         <f aca="false">$D$283*E284</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F285" s="15" t="n">
         <f aca="false">$D$283*F284</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G285" s="15" t="n">
         <f aca="false">$D$283*G284</f>
@@ -53744,7 +53744,7 @@
       </c>
       <c r="E286" s="20" t="n">
         <f aca="false">E282*E285</f>
-        <v>354.703044869172</v>
+        <v>354.703044869173</v>
       </c>
       <c r="F286" s="20" t="n">
         <f aca="false">F282*F285</f>
@@ -53752,7 +53752,7 @@
       </c>
       <c r="G286" s="20" t="n">
         <f aca="false">G282*G285</f>
-        <v>549.937653360093</v>
+        <v>549.937653360094</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53893,7 +53893,7 @@
       </c>
       <c r="E293" s="15" t="n">
         <f aca="false">E292/D292-1</f>
-        <v>0.316600251028347</v>
+        <v>0.316600251028349</v>
       </c>
       <c r="F293" s="15" t="n">
         <f aca="false">F292/E292-1</f>
@@ -53973,15 +53973,15 @@
       </c>
       <c r="E296" s="19" t="n">
         <f aca="false">(E286+E290)/fx/E279*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F296" s="19" t="n">
         <f aca="false">(F286+F290)/fx/F279*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G296" s="19" t="n">
         <f aca="false">(G286+G290)/fx/G279*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54021,11 +54021,11 @@
       </c>
       <c r="E299" s="20" t="n">
         <f aca="false">$D$298*E292+d_ai*E286</f>
-        <v>367.457404766332</v>
+        <v>367.457404766333</v>
       </c>
       <c r="F299" s="20" t="n">
         <f aca="false">$D$298*F292+d_ai*F286</f>
-        <v>446.094735723176</v>
+        <v>446.094735723177</v>
       </c>
       <c r="G299" s="20" t="n">
         <f aca="false">$D$298*G292+d_ai*G286</f>
@@ -54077,11 +54077,11 @@
       </c>
       <c r="E301" s="20" t="n">
         <f aca="false">D301*(1+MAX(0,phi*E293))</f>
-        <v>177.870649719095</v>
+        <v>177.870649719096</v>
       </c>
       <c r="F301" s="20" t="n">
         <f aca="false">E301*(1+MAX(0,phi*F293))</f>
-        <v>206.571969623614</v>
+        <v>206.571969623615</v>
       </c>
       <c r="G301" s="20" t="n">
         <f aca="false">F301*(1+MAX(0,phi*G293))</f>
@@ -54105,11 +54105,11 @@
       </c>
       <c r="E302" s="20" t="n">
         <f aca="false">E301+0*E292</f>
-        <v>177.870649719095</v>
+        <v>177.870649719096</v>
       </c>
       <c r="F302" s="20" t="n">
         <f aca="false">F301+0*F292</f>
-        <v>206.571969623614</v>
+        <v>206.571969623615</v>
       </c>
       <c r="G302" s="20" t="n">
         <f aca="false">G301+0*G292</f>
@@ -54301,15 +54301,15 @@
       </c>
       <c r="E309" s="21" t="n">
         <f aca="false">E307/E308</f>
-        <v>52.4754968202148</v>
+        <v>52.4754968202149</v>
       </c>
       <c r="F309" s="21" t="n">
         <f aca="false">F307/F308</f>
-        <v>65.7376053485118</v>
+        <v>65.7376053485119</v>
       </c>
       <c r="G309" s="21" t="n">
         <f aca="false">G307/G308</f>
-        <v>73.8796046416265</v>
+        <v>73.8796046416266</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54325,7 +54325,7 @@
       </c>
       <c r="E310" s="15" t="n">
         <f aca="false">E309/D309-1</f>
-        <v>0.385105347017793</v>
+        <v>0.385105347017795</v>
       </c>
       <c r="F310" s="15" t="n">
         <f aca="false">F309/E309-1</f>
@@ -54333,7 +54333,7 @@
       </c>
       <c r="G310" s="15" t="n">
         <f aca="false">G309/F309-1</f>
-        <v>0.123856037194379</v>
+        <v>0.123856037194378</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54381,7 +54381,7 @@
       </c>
       <c r="D316" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E316" s="21" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -54477,7 +54477,7 @@
       </c>
       <c r="D320" s="21" t="n">
         <f aca="false">D318*D319/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E320" s="21" t="n">
         <f aca="false">E318*E319/1000</f>
@@ -54525,7 +54525,7 @@
       </c>
       <c r="D322" s="15" t="n">
         <f aca="false">a26_aip/D321</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H322" s="8" t="s">
         <v>418</v>
@@ -54564,15 +54564,15 @@
       </c>
       <c r="D324" s="15" t="n">
         <f aca="false">$D$322*D323</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E324" s="15" t="n">
         <f aca="false">$D$322*E323</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F324" s="15" t="n">
         <f aca="false">$D$322*F323</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G324" s="15" t="n">
         <f aca="false">$D$322*G323</f>
@@ -54596,15 +54596,15 @@
       </c>
       <c r="E325" s="20" t="n">
         <f aca="false">E321*E324</f>
-        <v>532.054567303758</v>
+        <v>532.054567303759</v>
       </c>
       <c r="F325" s="20" t="n">
         <f aca="false">F321*F324</f>
-        <v>724.136958181968</v>
+        <v>724.136958181969</v>
       </c>
       <c r="G325" s="20" t="n">
         <f aca="false">G321*G324</f>
-        <v>824.90648004014</v>
+        <v>824.906480040141</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54665,11 +54665,11 @@
       </c>
       <c r="E329" s="20" t="n">
         <f aca="false">E318*$D$327*E328</f>
-        <v>222.138167017004</v>
+        <v>222.138167017005</v>
       </c>
       <c r="F329" s="20" t="n">
         <f aca="false">F318*$D$327*F328</f>
-        <v>294.385429125163</v>
+        <v>294.385429125164</v>
       </c>
       <c r="G329" s="20" t="n">
         <f aca="false">G318*$D$327*G328</f>
@@ -54745,7 +54745,7 @@
       </c>
       <c r="E332" s="15" t="n">
         <f aca="false">E331/D331-1</f>
-        <v>0.648950376542521</v>
+        <v>0.648950376542522</v>
       </c>
       <c r="F332" s="15" t="n">
         <f aca="false">F331/E331-1</f>
@@ -54781,7 +54781,7 @@
       </c>
       <c r="G333" s="15" t="n">
         <f aca="false">G325/G331</f>
-        <v>0.481467336082422</v>
+        <v>0.481467336082423</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54825,15 +54825,15 @@
       </c>
       <c r="E335" s="19" t="n">
         <f aca="false">(E325+E329)/fx/E318*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F335" s="19" t="n">
         <f aca="false">(F325+F329)/fx/F318*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G335" s="19" t="n">
         <f aca="false">(G325+G329)/fx/G318*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54873,15 +54873,15 @@
       </c>
       <c r="E338" s="20" t="n">
         <f aca="false">$D$337*E331+d_ai*E325</f>
-        <v>467.239970575962</v>
+        <v>467.239970575963</v>
       </c>
       <c r="F338" s="20" t="n">
         <f aca="false">$D$337*F331+d_ai*F325</f>
-        <v>580.998660182551</v>
+        <v>580.998660182552</v>
       </c>
       <c r="G338" s="20" t="n">
         <f aca="false">$D$337*G331+d_ai*G325</f>
-        <v>649.333344234558</v>
+        <v>649.333344234559</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54929,7 +54929,7 @@
       </c>
       <c r="E340" s="20" t="n">
         <f aca="false">D340*(1+MAX(0,phi*E332))</f>
-        <v>215.605440531636</v>
+        <v>215.605440531637</v>
       </c>
       <c r="F340" s="20" t="n">
         <f aca="false">E340*(1+MAX(0,phi*F332))</f>
@@ -54937,7 +54937,7 @@
       </c>
       <c r="G340" s="20" t="n">
         <f aca="false">F340*(1+MAX(0,phi*G332))</f>
-        <v>279.127223734532</v>
+        <v>279.127223734533</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54957,7 +54957,7 @@
       </c>
       <c r="E341" s="20" t="n">
         <f aca="false">E340+0*E331</f>
-        <v>215.605440531636</v>
+        <v>215.605440531637</v>
       </c>
       <c r="F341" s="20" t="n">
         <f aca="false">F340+0*F331</f>
@@ -54965,7 +54965,7 @@
       </c>
       <c r="G341" s="20" t="n">
         <f aca="false">G340+0*G331</f>
-        <v>279.127223734532</v>
+        <v>279.127223734533</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55017,11 +55017,11 @@
       </c>
       <c r="F343" s="15" t="n">
         <f aca="false">F342/F331</f>
-        <v>0.211828861221765</v>
+        <v>0.211828861221766</v>
       </c>
       <c r="G343" s="15" t="n">
         <f aca="false">G342/G331</f>
-        <v>0.216075590326169</v>
+        <v>0.21607559032617</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55101,7 +55101,7 @@
       </c>
       <c r="F346" s="20" t="n">
         <f aca="false">(F342+F344)*F345</f>
-        <v>230.067199007922</v>
+        <v>230.067199007923</v>
       </c>
       <c r="G346" s="20" t="n">
         <f aca="false">(G342+G344)*G345</f>
@@ -55157,7 +55157,7 @@
       </c>
       <c r="F348" s="21" t="n">
         <f aca="false">F346/F347</f>
-        <v>88.553217298673</v>
+        <v>88.5532172986731</v>
       </c>
       <c r="G348" s="21" t="n">
         <f aca="false">G346/G347</f>
@@ -55177,7 +55177,7 @@
       </c>
       <c r="E349" s="15" t="n">
         <f aca="false">E348/D348-1</f>
-        <v>0.820067219327902</v>
+        <v>0.820067219327904</v>
       </c>
       <c r="F349" s="15" t="n">
         <f aca="false">F348/E348-1</f>
@@ -55233,7 +55233,7 @@
       </c>
       <c r="D355" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E355" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55329,7 +55329,7 @@
       </c>
       <c r="D359" s="21" t="n">
         <f aca="false">D357*D358/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E359" s="21" t="n">
         <f aca="false">E357*E358/1000</f>
@@ -55377,7 +55377,7 @@
       </c>
       <c r="D361" s="15" t="n">
         <f aca="false">a26_aip/D360</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H361" s="8" t="s">
         <v>418</v>
@@ -55416,15 +55416,15 @@
       </c>
       <c r="D363" s="15" t="n">
         <f aca="false">$D$361*D362</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E363" s="15" t="n">
         <f aca="false">$D$361*E362</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F363" s="15" t="n">
         <f aca="false">$D$361*F362</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G363" s="15" t="n">
         <f aca="false">$D$361*G362</f>
@@ -55448,15 +55448,15 @@
       </c>
       <c r="E364" s="20" t="n">
         <f aca="false">E360*E363</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F364" s="20" t="n">
         <f aca="false">F360*F363</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G364" s="20" t="n">
         <f aca="false">G360*G363</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55521,7 +55521,7 @@
       </c>
       <c r="F368" s="20" t="n">
         <f aca="false">F357*$D$366*F367</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G368" s="20" t="n">
         <f aca="false">G357*$D$366*G367</f>
@@ -55597,7 +55597,7 @@
       </c>
       <c r="E371" s="15" t="n">
         <f aca="false">E370/D370-1</f>
-        <v>0.445875313785434</v>
+        <v>0.445875313785435</v>
       </c>
       <c r="F371" s="15" t="n">
         <f aca="false">F370/E370-1</f>
@@ -55605,7 +55605,7 @@
       </c>
       <c r="G371" s="15" t="n">
         <f aca="false">G370/F370-1</f>
-        <v>0.0991373579321482</v>
+        <v>0.099137357932148</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55653,15 +55653,15 @@
       </c>
       <c r="E373" s="15" t="n">
         <f aca="false">(E364+E368)/E370</f>
-        <v>0.574652119628577</v>
+        <v>0.574652119628578</v>
       </c>
       <c r="F373" s="15" t="n">
         <f aca="false">(F364+F368)/F370</f>
-        <v>0.645957725821228</v>
+        <v>0.645957725821229</v>
       </c>
       <c r="G373" s="15" t="n">
         <f aca="false">(G364+G368)/G370</f>
-        <v>0.677890782599869</v>
+        <v>0.67789078259987</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55677,15 +55677,15 @@
       </c>
       <c r="E374" s="19" t="n">
         <f aca="false">(E364+E368)/fx/E357*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F374" s="19" t="n">
         <f aca="false">(F364+F368)/fx/F357*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G374" s="19" t="n">
         <f aca="false">(G364+G368)/fx/G357*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55725,11 +55725,11 @@
       </c>
       <c r="E377" s="20" t="n">
         <f aca="false">$D$376*E370+d_ai*E364</f>
-        <v>407.845351455275</v>
+        <v>407.845351455276</v>
       </c>
       <c r="F377" s="20" t="n">
         <f aca="false">$D$376*F370+d_ai*F364</f>
-        <v>495.648748079638</v>
+        <v>495.648748079639</v>
       </c>
       <c r="G377" s="20" t="n">
         <f aca="false">$D$376*G370+d_ai*G364</f>
@@ -55757,7 +55757,7 @@
       </c>
       <c r="F378" s="15" t="n">
         <f aca="false">F377/F370</f>
-        <v>0.377214846258396</v>
+        <v>0.377214846258397</v>
       </c>
       <c r="G378" s="15" t="n">
         <f aca="false">G377/G370</f>
@@ -55837,7 +55837,7 @@
       </c>
       <c r="E381" s="20" t="n">
         <f aca="false">E377-E380</f>
-        <v>215.296905412589</v>
+        <v>215.29690541259</v>
       </c>
       <c r="F381" s="20" t="n">
         <f aca="false">F377-F380</f>
@@ -55845,7 +55845,7 @@
       </c>
       <c r="G381" s="20" t="n">
         <f aca="false">G377-G380</f>
-        <v>305.414078034681</v>
+        <v>305.414078034682</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56009,11 +56009,11 @@
       </c>
       <c r="F387" s="21" t="n">
         <f aca="false">F385/F386</f>
-        <v>74.3832258148109</v>
+        <v>74.383225814811</v>
       </c>
       <c r="G387" s="21" t="n">
         <f aca="false">G385/G386</f>
-        <v>83.2371555036046</v>
+        <v>83.2371555036047</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56029,7 +56029,7 @@
       </c>
       <c r="E388" s="15" t="n">
         <f aca="false">E387/D387-1</f>
-        <v>0.565336388998151</v>
+        <v>0.565336388998153</v>
       </c>
       <c r="F388" s="15" t="n">
         <f aca="false">F387/E387-1</f>
@@ -56085,7 +56085,7 @@
       </c>
       <c r="D394" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E394" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56181,7 +56181,7 @@
       </c>
       <c r="D398" s="21" t="n">
         <f aca="false">D396*D397/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E398" s="21" t="n">
         <f aca="false">E396*E397/1000</f>
@@ -56229,7 +56229,7 @@
       </c>
       <c r="D400" s="15" t="n">
         <f aca="false">a26_aip/D399</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H400" s="8" t="s">
         <v>418</v>
@@ -56268,15 +56268,15 @@
       </c>
       <c r="D402" s="15" t="n">
         <f aca="false">$D$400*D401</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E402" s="15" t="n">
         <f aca="false">$D$400*E401</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F402" s="15" t="n">
         <f aca="false">$D$400*F401</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G402" s="15" t="n">
         <f aca="false">$D$400*G401</f>
@@ -56300,15 +56300,15 @@
       </c>
       <c r="E403" s="20" t="n">
         <f aca="false">E399*E402</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F403" s="20" t="n">
         <f aca="false">F399*F402</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G403" s="20" t="n">
         <f aca="false">G399*G402</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56373,7 +56373,7 @@
       </c>
       <c r="F407" s="20" t="n">
         <f aca="false">F396*$D$405*F406</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G407" s="20" t="n">
         <f aca="false">G396*$D$405*G406</f>
@@ -56449,7 +56449,7 @@
       </c>
       <c r="E410" s="15" t="n">
         <f aca="false">E409/D409-1</f>
-        <v>0.507375313785434</v>
+        <v>0.507375313785435</v>
       </c>
       <c r="F410" s="15" t="n">
         <f aca="false">F409/E409-1</f>
@@ -56477,7 +56477,7 @@
       </c>
       <c r="E411" s="15" t="n">
         <f aca="false">E403/E409</f>
-        <v>0.388855538164261</v>
+        <v>0.388855538164262</v>
       </c>
       <c r="F411" s="15" t="n">
         <f aca="false">F403/F409</f>
@@ -56529,15 +56529,15 @@
       </c>
       <c r="E413" s="19" t="n">
         <f aca="false">(E403+E407)/fx/E396*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F413" s="19" t="n">
         <f aca="false">(F403+F407)/fx/F396*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G413" s="19" t="n">
         <f aca="false">(G403+G407)/fx/G396*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56577,15 +56577,15 @@
       </c>
       <c r="E416" s="20" t="n">
         <f aca="false">$D$415*E409+d_ai*E403</f>
-        <v>423.684245148395</v>
+        <v>423.684245148396</v>
       </c>
       <c r="F416" s="20" t="n">
         <f aca="false">$D$415*F409+d_ai*F403</f>
-        <v>528.91042483519</v>
+        <v>528.910424835191</v>
       </c>
       <c r="G416" s="20" t="n">
         <f aca="false">$D$415*G409+d_ai*G403</f>
-        <v>595.311814413322</v>
+        <v>595.311814413323</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56637,7 +56637,7 @@
       </c>
       <c r="F418" s="20" t="n">
         <f aca="false">E418*(1+MAX(0,phi*F410))</f>
-        <v>237.532430420257</v>
+        <v>237.532430420258</v>
       </c>
       <c r="G418" s="20" t="n">
         <f aca="false">F418*(1+MAX(0,phi*G410))</f>
@@ -56665,7 +56665,7 @@
       </c>
       <c r="F419" s="20" t="n">
         <f aca="false">F418+0*F409</f>
-        <v>237.532430420257</v>
+        <v>237.532430420258</v>
       </c>
       <c r="G419" s="20" t="n">
         <f aca="false">G418+0*G409</f>
@@ -56689,7 +56689,7 @@
       </c>
       <c r="E420" s="20" t="n">
         <f aca="false">E416-E419</f>
-        <v>224.153133967909</v>
+        <v>224.15313396791</v>
       </c>
       <c r="F420" s="20" t="n">
         <f aca="false">F416-F419</f>
@@ -56697,7 +56697,7 @@
       </c>
       <c r="G420" s="20" t="n">
         <f aca="false">G416-G419</f>
-        <v>334.182668585462</v>
+        <v>334.182668585463</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56801,7 +56801,7 @@
       </c>
       <c r="E424" s="20" t="n">
         <f aca="false">(E420+E422)*E423</f>
-        <v>160.185662437857</v>
+        <v>160.185662437858</v>
       </c>
       <c r="F424" s="20" t="n">
         <f aca="false">(F420+F422)*F423</f>
@@ -56857,15 +56857,15 @@
       </c>
       <c r="E426" s="21" t="n">
         <f aca="false">E424/E425</f>
-        <v>61.6557068333022</v>
+        <v>61.6557068333023</v>
       </c>
       <c r="F426" s="21" t="n">
         <f aca="false">F424/F425</f>
-        <v>79.5094235451528</v>
+        <v>79.5094235451529</v>
       </c>
       <c r="G426" s="21" t="n">
         <f aca="false">G424/G425</f>
-        <v>90.8775769559871</v>
+        <v>90.8775769559872</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56881,11 +56881,11 @@
       </c>
       <c r="E427" s="15" t="n">
         <f aca="false">E426/D426-1</f>
-        <v>0.627419545955979</v>
+        <v>0.62741954595598</v>
       </c>
       <c r="F427" s="15" t="n">
         <f aca="false">F426/E426-1</f>
-        <v>0.289571195090203</v>
+        <v>0.289571195090204</v>
       </c>
       <c r="G427" s="15" t="n">
         <f aca="false">G426/F426-1</f>
@@ -56937,7 +56937,7 @@
       </c>
       <c r="D433" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E433" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57033,7 +57033,7 @@
       </c>
       <c r="D437" s="21" t="n">
         <f aca="false">D435*D436/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E437" s="21" t="n">
         <f aca="false">E435*E436/1000</f>
@@ -57081,7 +57081,7 @@
       </c>
       <c r="D439" s="15" t="n">
         <f aca="false">a26_aip/D438</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H439" s="8" t="s">
         <v>418</v>
@@ -57120,15 +57120,15 @@
       </c>
       <c r="D441" s="15" t="n">
         <f aca="false">$D$439*D440</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E441" s="15" t="n">
         <f aca="false">$D$439*E440</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F441" s="15" t="n">
         <f aca="false">$D$439*F440</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G441" s="15" t="n">
         <f aca="false">$D$439*G440</f>
@@ -57152,15 +57152,15 @@
       </c>
       <c r="E442" s="20" t="n">
         <f aca="false">E438*E441</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F442" s="20" t="n">
         <f aca="false">F438*F441</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G442" s="20" t="n">
         <f aca="false">G438*G441</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57225,7 +57225,7 @@
       </c>
       <c r="F446" s="20" t="n">
         <f aca="false">F435*$D$444*F445</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G446" s="20" t="n">
         <f aca="false">G435*$D$444*G445</f>
@@ -57301,7 +57301,7 @@
       </c>
       <c r="E449" s="15" t="n">
         <f aca="false">E448/D448-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F449" s="15" t="n">
         <f aca="false">F448/E448-1</f>
@@ -57333,7 +57333,7 @@
       </c>
       <c r="F450" s="15" t="n">
         <f aca="false">F442/F448</f>
-        <v>0.441588811974854</v>
+        <v>0.441588811974855</v>
       </c>
       <c r="G450" s="15" t="n">
         <f aca="false">G442/G448</f>
@@ -57381,15 +57381,15 @@
       </c>
       <c r="E452" s="19" t="n">
         <f aca="false">(E442+E446)/fx/E435*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F452" s="19" t="n">
         <f aca="false">(F442+F446)/fx/F435*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G452" s="19" t="n">
         <f aca="false">(G442+G446)/fx/G435*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57437,7 +57437,7 @@
       </c>
       <c r="G455" s="20" t="n">
         <f aca="false">$D$454*G448+d_ai_lo*G442</f>
-        <v>559.952747916109</v>
+        <v>559.95274791611</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57493,7 +57493,7 @@
       </c>
       <c r="G457" s="20" t="n">
         <f aca="false">F457*(1+MAX(0,phi*G449))</f>
-        <v>251.534257139136</v>
+        <v>251.534257139137</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57521,7 +57521,7 @@
       </c>
       <c r="G458" s="20" t="n">
         <f aca="false">G457+0*G448</f>
-        <v>251.534257139136</v>
+        <v>251.534257139137</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57661,7 +57661,7 @@
       </c>
       <c r="G463" s="20" t="n">
         <f aca="false">(G459+G461)*G462</f>
-        <v>218.328758636111</v>
+        <v>218.328758636112</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57713,11 +57713,11 @@
       </c>
       <c r="F465" s="21" t="n">
         <f aca="false">F463/F464</f>
-        <v>74.4991331455169</v>
+        <v>74.499133145517</v>
       </c>
       <c r="G465" s="21" t="n">
         <f aca="false">G463/G464</f>
-        <v>84.0350736194573</v>
+        <v>84.0350736194574</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57733,7 +57733,7 @@
       </c>
       <c r="E466" s="15" t="n">
         <f aca="false">E465/D465-1</f>
-        <v>0.560031797890063</v>
+        <v>0.560031797890064</v>
       </c>
       <c r="F466" s="15" t="n">
         <f aca="false">F465/E465-1</f>
@@ -57789,7 +57789,7 @@
       </c>
       <c r="D472" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E472" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57885,7 +57885,7 @@
       </c>
       <c r="D476" s="21" t="n">
         <f aca="false">D474*D475/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E476" s="21" t="n">
         <f aca="false">E474*E475/1000</f>
@@ -57933,7 +57933,7 @@
       </c>
       <c r="D478" s="15" t="n">
         <f aca="false">a26_aip/D477</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H478" s="8" t="s">
         <v>418</v>
@@ -57972,15 +57972,15 @@
       </c>
       <c r="D480" s="15" t="n">
         <f aca="false">$D$478*D479</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E480" s="15" t="n">
         <f aca="false">$D$478*E479</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F480" s="15" t="n">
         <f aca="false">$D$478*F479</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G480" s="15" t="n">
         <f aca="false">$D$478*G479</f>
@@ -58004,15 +58004,15 @@
       </c>
       <c r="E481" s="20" t="n">
         <f aca="false">E477*E480</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F481" s="20" t="n">
         <f aca="false">F477*F480</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G481" s="20" t="n">
         <f aca="false">G477*G480</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58077,7 +58077,7 @@
       </c>
       <c r="F485" s="20" t="n">
         <f aca="false">F474*$D$483*F484</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G485" s="20" t="n">
         <f aca="false">G474*$D$483*G484</f>
@@ -58153,7 +58153,7 @@
       </c>
       <c r="E488" s="15" t="n">
         <f aca="false">E487/D487-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F488" s="15" t="n">
         <f aca="false">F487/E487-1</f>
@@ -58185,7 +58185,7 @@
       </c>
       <c r="F489" s="15" t="n">
         <f aca="false">F481/F487</f>
-        <v>0.441588811974854</v>
+        <v>0.441588811974855</v>
       </c>
       <c r="G489" s="15" t="n">
         <f aca="false">G481/G487</f>
@@ -58233,15 +58233,15 @@
       </c>
       <c r="E491" s="19" t="n">
         <f aca="false">(E481+E485)/fx/E474*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F491" s="19" t="n">
         <f aca="false">(F481+F485)/fx/F474*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G491" s="19" t="n">
         <f aca="false">(G481+G485)/fx/G474*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58289,7 +58289,7 @@
       </c>
       <c r="G494" s="20" t="n">
         <f aca="false">$D$493*G487+d_ai_hi*G481</f>
-        <v>583.382279900355</v>
+        <v>583.382279900356</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58345,7 +58345,7 @@
       </c>
       <c r="G496" s="20" t="n">
         <f aca="false">F496*(1+MAX(0,phi*G488))</f>
-        <v>251.534257139136</v>
+        <v>251.534257139137</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58373,7 +58373,7 @@
       </c>
       <c r="G497" s="20" t="n">
         <f aca="false">G496+0*G487</f>
-        <v>251.534257139136</v>
+        <v>251.534257139137</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58561,15 +58561,15 @@
       </c>
       <c r="E504" s="21" t="n">
         <f aca="false">E502/E503</f>
-        <v>62.3270853367013</v>
+        <v>62.3270853367014</v>
       </c>
       <c r="F504" s="21" t="n">
         <f aca="false">F502/F503</f>
-        <v>79.7714221706608</v>
+        <v>79.7714221706609</v>
       </c>
       <c r="G504" s="21" t="n">
         <f aca="false">G502/G503</f>
-        <v>90.2575369158684</v>
+        <v>90.2575369158685</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58585,15 +58585,15 @@
       </c>
       <c r="E505" s="15" t="n">
         <f aca="false">E504/D504-1</f>
-        <v>0.645140768455632</v>
+        <v>0.645140768455633</v>
       </c>
       <c r="F505" s="15" t="n">
         <f aca="false">F504/E504-1</f>
-        <v>0.279883725345447</v>
+        <v>0.279883725345446</v>
       </c>
       <c r="G505" s="15" t="n">
         <f aca="false">G504/F504-1</f>
-        <v>0.131452022038342</v>
+        <v>0.131452022038343</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58641,7 +58641,7 @@
       </c>
       <c r="D511" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E511" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58737,7 +58737,7 @@
       </c>
       <c r="D515" s="21" t="n">
         <f aca="false">D513*D514/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E515" s="21" t="n">
         <f aca="false">E513*E514/1000</f>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="D517" s="15" t="n">
         <f aca="false">a26_aip/D516</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H517" s="8" t="s">
         <v>418</v>
@@ -58824,15 +58824,15 @@
       </c>
       <c r="D519" s="15" t="n">
         <f aca="false">$D$517*D518</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="E519" s="15" t="n">
         <f aca="false">$D$517*E518</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="F519" s="15" t="n">
         <f aca="false">$D$517*F518</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G519" s="15" t="n">
         <f aca="false">$D$517*G518</f>
@@ -58856,15 +58856,15 @@
       </c>
       <c r="E520" s="20" t="n">
         <f aca="false">E516*E519</f>
-        <v>443.378806086465</v>
+        <v>443.378806086466</v>
       </c>
       <c r="F520" s="20" t="n">
         <f aca="false">F516*F519</f>
-        <v>603.44746515164</v>
+        <v>603.447465151641</v>
       </c>
       <c r="G520" s="20" t="n">
         <f aca="false">G516*G519</f>
-        <v>687.422066700117</v>
+        <v>687.422066700118</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58929,7 +58929,7 @@
       </c>
       <c r="F524" s="20" t="n">
         <f aca="false">F513*$D$522*F523</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G524" s="20" t="n">
         <f aca="false">G513*$D$522*G523</f>
@@ -59005,7 +59005,7 @@
       </c>
       <c r="E527" s="15" t="n">
         <f aca="false">E526/D526-1</f>
-        <v>0.482775313785434</v>
+        <v>0.482775313785435</v>
       </c>
       <c r="F527" s="15" t="n">
         <f aca="false">F526/E526-1</f>
@@ -59037,7 +59037,7 @@
       </c>
       <c r="F528" s="15" t="n">
         <f aca="false">F520/F526</f>
-        <v>0.441588811974854</v>
+        <v>0.441588811974855</v>
       </c>
       <c r="G528" s="15" t="n">
         <f aca="false">G520/G526</f>
@@ -59085,15 +59085,15 @@
       </c>
       <c r="E530" s="19" t="n">
         <f aca="false">(E520+E524)/fx/E513*1000</f>
-        <v>471.595702572219</v>
+        <v>471.59570257222</v>
       </c>
       <c r="F530" s="19" t="n">
         <f aca="false">(F520+F524)/fx/F513*1000</f>
-        <v>502.423682986704</v>
+        <v>502.423682986705</v>
       </c>
       <c r="G530" s="19" t="n">
         <f aca="false">(G520+G524)/fx/G513*1000</f>
-        <v>508.737441946525</v>
+        <v>508.737441946526</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59133,7 +59133,7 @@
       </c>
       <c r="E533" s="20" t="n">
         <f aca="false">$D$532*E526+d_ai*E520</f>
-        <v>417.348687671147</v>
+        <v>417.348687671148</v>
       </c>
       <c r="F533" s="20" t="n">
         <f aca="false">$D$532*F526+d_ai*F520</f>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="G533" s="20" t="n">
         <f aca="false">$D$532*G526+d_ai*G520</f>
-        <v>571.667513908232</v>
+        <v>571.667513908233</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59197,7 +59197,7 @@
       </c>
       <c r="G535" s="20" t="n">
         <f aca="false">F535*(1+MAX(0,phi*G527))</f>
-        <v>251.534257139136</v>
+        <v>251.534257139137</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59253,7 +59253,7 @@
       </c>
       <c r="G537" s="20" t="n">
         <f aca="false">G533-G536</f>
-        <v>289.7830323924</v>
+        <v>289.783032392401</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59361,7 +59361,7 @@
       </c>
       <c r="F541" s="20" t="n">
         <f aca="false">(F537+F539)*F540</f>
-        <v>181.544414802956</v>
+        <v>181.544414802957</v>
       </c>
       <c r="G541" s="20" t="n">
         <f aca="false">(G537+G539)*G540</f>
@@ -59413,7 +59413,7 @@
       </c>
       <c r="E543" s="21" t="n">
         <f aca="false">E541/E542</f>
-        <v>54.757312462751</v>
+        <v>54.7573124627511</v>
       </c>
       <c r="F543" s="21" t="n">
         <f aca="false">F541/F542</f>
@@ -59421,7 +59421,7 @@
       </c>
       <c r="G543" s="21" t="n">
         <f aca="false">G541/G542</f>
-        <v>79.0858302505427</v>
+        <v>79.0858302505428</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59437,7 +59437,7 @@
       </c>
       <c r="E544" s="15" t="n">
         <f aca="false">E543/D543-1</f>
-        <v>0.445334506128265</v>
+        <v>0.445334506128266</v>
       </c>
       <c r="F544" s="15" t="n">
         <f aca="false">F543/E543-1</f>
@@ -59493,7 +59493,7 @@
       </c>
       <c r="D550" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E550" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59589,7 +59589,7 @@
       </c>
       <c r="D554" s="21" t="n">
         <f aca="false">D552*D553/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E554" s="21" t="n">
         <f aca="false">E552*E553/1000</f>
@@ -59708,7 +59708,7 @@
       </c>
       <c r="E559" s="20" t="n">
         <f aca="false">E555*E558</f>
-        <v>230.215918544895</v>
+        <v>230.215918544896</v>
       </c>
       <c r="F559" s="20" t="n">
         <f aca="false">F555*F558</f>
@@ -59781,7 +59781,7 @@
       </c>
       <c r="F563" s="20" t="n">
         <f aca="false">F552*$D$561*F562</f>
-        <v>245.321190937636</v>
+        <v>245.321190937637</v>
       </c>
       <c r="G563" s="20" t="n">
         <f aca="false">G552*$D$561*G562</f>
@@ -59861,7 +59861,7 @@
       </c>
       <c r="F566" s="15" t="n">
         <f aca="false">F565/E565-1</f>
-        <v>0.171498682535416</v>
+        <v>0.171498682535417</v>
       </c>
       <c r="G566" s="15" t="n">
         <f aca="false">G565/F565-1</f>
@@ -59917,7 +59917,7 @@
       </c>
       <c r="F568" s="15" t="n">
         <f aca="false">(F559+F563)/F565</f>
-        <v>0.472768641895038</v>
+        <v>0.472768641895039</v>
       </c>
       <c r="G568" s="15" t="n">
         <f aca="false">(G559+G563)/G565</f>
@@ -59937,11 +59937,11 @@
       </c>
       <c r="E569" s="19" t="n">
         <f aca="false">(E559+E563)/fx/E552*1000</f>
-        <v>311.647142256757</v>
+        <v>311.647142256758</v>
       </c>
       <c r="F569" s="19" t="n">
         <f aca="false">(F559+F563)/fx/F552*1000</f>
-        <v>330.689439279577</v>
+        <v>330.689439279578</v>
       </c>
       <c r="G569" s="19" t="n">
         <f aca="false">(G559+G563)/fx/G552*1000</f>
@@ -59985,15 +59985,15 @@
       </c>
       <c r="E572" s="20" t="n">
         <f aca="false">$D$571*E565+d_ai*E559</f>
-        <v>371.930292069246</v>
+        <v>371.930292069247</v>
       </c>
       <c r="F572" s="20" t="n">
         <f aca="false">$D$571*F565+d_ai*F559</f>
-        <v>439.206314853896</v>
+        <v>439.206314853897</v>
       </c>
       <c r="G572" s="20" t="n">
         <f aca="false">$D$571*G565+d_ai*G559</f>
-        <v>482.93290701751</v>
+        <v>482.932907017511</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60105,7 +60105,7 @@
       </c>
       <c r="G576" s="20" t="n">
         <f aca="false">G572-G575</f>
-        <v>262.588261624444</v>
+        <v>262.588261624445</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60265,7 +60265,7 @@
       </c>
       <c r="E582" s="21" t="n">
         <f aca="false">E580/E581</f>
-        <v>53.1546698485424</v>
+        <v>53.1546698485425</v>
       </c>
       <c r="F582" s="21" t="n">
         <f aca="false">F580/F581</f>
@@ -60273,7 +60273,7 @@
       </c>
       <c r="G582" s="21" t="n">
         <f aca="false">G580/G581</f>
-        <v>71.8633870932613</v>
+        <v>71.8633870932614</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60289,11 +60289,11 @@
       </c>
       <c r="E583" s="15" t="n">
         <f aca="false">E582/D582-1</f>
-        <v>0.403032308172822</v>
+        <v>0.403032308172823</v>
       </c>
       <c r="F583" s="15" t="n">
         <f aca="false">F582/E582-1</f>
-        <v>0.212894360189794</v>
+        <v>0.212894360189793</v>
       </c>
       <c r="G583" s="15" t="n">
         <f aca="false">G582/F582-1</f>
@@ -60334,7 +60334,7 @@
       </c>
       <c r="C588" s="19" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>999.125303827977</v>
+        <v>999.125303827979</v>
       </c>
       <c r="D588" s="19" t="n">
         <f aca="false">Val!B115</f>
@@ -60358,7 +60358,7 @@
       </c>
       <c r="C589" s="19" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
-        <v>862.638381288533</v>
+        <v>862.638381288534</v>
       </c>
       <c r="D589" s="19" t="n">
         <f aca="false">Val!B115</f>
@@ -60366,7 +60366,7 @@
       </c>
       <c r="E589" s="19" t="n">
         <f aca="false">tp_w_dcf*C589+(1-tp_w_dcf)*D589</f>
-        <v>1145.52676808533</v>
+        <v>1145.52676808534</v>
       </c>
       <c r="F589" s="15" t="n">
         <f aca="false">E589/E$588-1</f>
@@ -60394,7 +60394,7 @@
       </c>
       <c r="F590" s="15" t="n">
         <f aca="false">E590/E$588-1</f>
-        <v>0.07871301036868</v>
+        <v>0.0787130103686802</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60430,7 +60430,7 @@
       </c>
       <c r="C592" s="19" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>952.846916241758</v>
+        <v>952.846916241759</v>
       </c>
       <c r="D592" s="19" t="n">
         <f aca="false">Val!B115</f>
@@ -60442,7 +60442,7 @@
       </c>
       <c r="F592" s="15" t="n">
         <f aca="false">E592/E$588-1</f>
-        <v>-0.0190638996026499</v>
+        <v>-0.0190638996026498</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60454,7 +60454,7 @@
       </c>
       <c r="C593" s="19" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>999.125303827977</v>
+        <v>999.125303827979</v>
       </c>
       <c r="D593" s="19" t="n">
         <f aca="false">Val!B115</f>
@@ -60478,7 +60478,7 @@
       </c>
       <c r="C594" s="19" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>999.125303827977</v>
+        <v>999.125303827979</v>
       </c>
       <c r="D594" s="19" t="n">
         <f aca="false">Val!B115</f>
@@ -60490,7 +60490,7 @@
       </c>
       <c r="F594" s="15" t="n">
         <f aca="false">E594/E$588-1</f>
-        <v>-0.106104888883854</v>
+        <v>-0.106104888883853</v>
       </c>
     </row>
   </sheetData>
